--- a/data/result.xlsx
+++ b/data/result.xlsx
@@ -466,7 +466,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>model_filters</t>
+          <t>context_filters</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -516,72 +516,72 @@
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
+          <t>response_time</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
           <t>sentence_count</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>word_count</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>avg_sentence_len</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>unique_word_ratio</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>faithfulness_score_entailment</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>faithfulness_score_neutral</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>faithfulness_score_contradiction</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>answer_correctness_literal</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>answer_correctness_neural</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>answer_relevance</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>jaccard_similarity</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>cosine_tag_answer</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>relevance</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>response_time</t>
         </is>
       </c>
     </row>
@@ -623,7 +623,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['https://www.hse.ru/org/hse/elective_courses/MN_OI', 'file_280.docx', 'Учебный процесс', 'Траектории обучения', 'https://electives.hse.ru/', 'file_193.docx', 'Деньги', 'Учебный процесс', 'Практическая подготовка', 'ГИА', 'Траектории обучения', 'Английский язык', 'Цифровые компетенции', 'Онлайн-обучение', 'Дополнительное образование', 'https://www.hse.ru/docs/289423580.html', 'file_21.docx', 'Учебный процесс', 'https://www.hse.ru/docs/490481113.html', 'file_26.docx', 'Учебный процесс', 'Траектории обучения']</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -641,19 +641,19 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['https://www.hse.ru/org/hse/elective_courses/MN_OI', 'https://electives.hse', 'https://www.hse.ru/docs/289423580.html', 'https://www.hse.ru/docs/490481113.html']</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>3</v>
       </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O2" t="n">
         <v>79</v>
       </c>
-      <c r="P2" t="n">
+      <c r="P2" t="b">
         <v>1</v>
       </c>
       <c r="Q2" t="inlineStr">
@@ -662,46 +662,46 @@
         </is>
       </c>
       <c r="R2" t="n">
+        <v>8.412186999999999</v>
+      </c>
+      <c r="S2" t="n">
         <v>4</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>72</v>
       </c>
-      <c r="T2" t="n">
+      <c r="U2" t="n">
         <v>18</v>
       </c>
-      <c r="U2" t="n">
+      <c r="V2" t="n">
         <v>0.9166666666666666</v>
       </c>
-      <c r="V2" t="n">
+      <c r="W2" t="n">
         <v>0.6118826866149902</v>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>0.1876140832901001</v>
       </c>
-      <c r="X2" t="n">
+      <c r="Y2" t="n">
         <v>0.2005032300949097</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>29.3062528169179</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="AA2" t="n">
         <v>0.5740185379981995</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AB2" t="n">
         <v>0.3189123272895813</v>
       </c>
-      <c r="AB2" t="n">
-        <v>0</v>
-      </c>
       <c r="AC2" t="n">
+        <v>0.05882352941176471</v>
+      </c>
+      <c r="AD2" t="n">
         <v>0.3276387453079224</v>
       </c>
-      <c r="AD2" t="b">
-        <v>1</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>8.412186999999999</v>
+      <c r="AE2" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -742,7 +742,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['https://www.hse.ru/studyspravka/plan', 'file_254.docx', 'Деньги', 'Учебный процесс', 'Практическая подготовка', 'Траектории обучения', 'Английский язык', 'Перемещения студентов / Изменения статусов студентов', 'Дополнительное образование', 'Социальные вопросы', 'https://www.hse.ru/studyspravka/kontr', 'file_270.docx', 'Деньги', 'Учебный процесс', 'Перемещения студентов / Изменения статусов студентов', 'https://www.hse.ru/docs/480101460.html', 'file_75.docx', 'Учебный процесс', 'Траектории обучения', 'Перемещения студентов / Изменения статусов студентов', 'https://www.hse.ru/docs/552116522.html', 'file_20.docx', 'Учебный процесс']</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -760,19 +760,19 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['https://www.hse.ru/studyspravka/plan', 'https://www.hse.ru/studyspravka/kontr', 'https://www.hse.ru/docs/480101460.html', 'https://www.hse.ru/docs/552116522.html']</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>3</v>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O3" t="n">
         <v>71</v>
       </c>
-      <c r="P3" t="n">
+      <c r="P3" t="b">
         <v>1</v>
       </c>
       <c r="Q3" t="inlineStr">
@@ -781,46 +781,46 @@
         </is>
       </c>
       <c r="R3" t="n">
+        <v>13.259808</v>
+      </c>
+      <c r="S3" t="n">
         <v>5</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>66</v>
       </c>
-      <c r="T3" t="n">
+      <c r="U3" t="n">
         <v>13.2</v>
       </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
         <v>0.8787878787878788</v>
       </c>
-      <c r="V3" t="n">
+      <c r="W3" t="n">
         <v>0.6489430069923401</v>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>0.1347694993019104</v>
       </c>
-      <c r="X3" t="n">
+      <c r="Y3" t="n">
         <v>0.2162874639034271</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>27.46260354420096</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="AA3" t="n">
         <v>0.6110109686851501</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="AB3" t="n">
         <v>0.3152807950973511</v>
       </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
       <c r="AC3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AD3" t="n">
         <v>0.3684489727020264</v>
       </c>
-      <c r="AD3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>13.259808</v>
+      <c r="AE3" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -861,7 +861,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['https://www.hse.ru/studyspravka/plan', 'file_254.docx', 'Деньги', 'Учебный процесс', 'Практическая подготовка', 'Траектории обучения', 'Английский язык', 'Перемещения студентов / Изменения статусов студентов', 'Дополнительное образование', 'Социальные вопросы', 'https://electives.hse.ru/kpv', 'file_394.docx', 'Деньги', 'Учебный процесс', 'Траектории обучения', 'Английский язык', 'Цифровые системы', 'Дополнительное образование', 'https://www.hse.ru/docs/490481113.html', 'file_26.docx', 'Учебный процесс', 'Траектории обучения', 'https://www.hse.ru/studyspravka/kontr', 'file_270.docx', 'Деньги', 'Учебный процесс', 'Перемещения студентов / Изменения статусов студентов']</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -879,19 +879,19 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['https://www.hse.ru/studyspravka/plan', 'https://electives.hse', 'https://www.hse.ru/docs/490481113.html', 'https://www.hse.ru/studyspravka/kontr']</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>3</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O4" t="n">
         <v>73</v>
       </c>
-      <c r="P4" t="n">
+      <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" t="inlineStr">
@@ -900,46 +900,46 @@
         </is>
       </c>
       <c r="R4" t="n">
+        <v>18.527903</v>
+      </c>
+      <c r="S4" t="n">
         <v>8</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>69</v>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
         <v>8.625</v>
       </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
         <v>0.8115942028985508</v>
       </c>
-      <c r="V4" t="n">
+      <c r="W4" t="n">
         <v>0.7002854347229004</v>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>0.218845397233963</v>
       </c>
-      <c r="X4" t="n">
+      <c r="Y4" t="n">
         <v>0.08086920529603958</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>22.23612969715292</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="AA4" t="n">
         <v>0.5656224489212036</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AB4" t="n">
         <v>0.3846144080162048</v>
       </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
       <c r="AC4" t="n">
+        <v>0.05882352941176471</v>
+      </c>
+      <c r="AD4" t="n">
         <v>0.3417143523693085</v>
       </c>
-      <c r="AD4" t="b">
-        <v>1</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>18.527903</v>
+      <c r="AE4" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -980,7 +980,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['https://www.hse.ru/studyspravka/plan', 'file_254.docx', 'Деньги', 'Учебный процесс', 'Практическая подготовка', 'Траектории обучения', 'Английский язык', 'Перемещения студентов / Изменения статусов студентов', 'Дополнительное образование', 'Социальные вопросы', 'https://electives.hse.ru/kpv', 'file_394.docx', 'Деньги', 'Учебный процесс', 'Траектории обучения', 'Английский язык', 'Цифровые системы', 'Дополнительное образование', 'https://www.hse.ru/docs/490481113.html', 'file_26.docx', 'Учебный процесс', 'Траектории обучения', 'https://www.hse.ru/studyspravka/kontr', 'file_270.docx', 'Деньги', 'Учебный процесс', 'Перемещения студентов / Изменения статусов студентов', 'https://www.hse.ru/studyspravka/plan', 'file_254.docx', 'Деньги', 'Учебный процесс', 'Практическая подготовка', 'Траектории обучения', 'Английский язык', 'Перемещения студентов / Изменения статусов студентов', 'Дополнительное образование', 'Социальные вопросы', 'https://www.hse.ru/org/hse/elective_courses/MN_OI', 'file_280.docx', 'Учебный процесс', 'Траектории обучения', 'https://electives.hse.ru/', 'file_193.docx', 'Деньги', 'Учебный процесс', 'Практическая подготовка', 'ГИА', 'Траектории обучения', 'Английский язык', 'Цифровые компетенции', 'Онлайн-обучение', 'Дополнительное образование', 'https://www.hse.ru/docs/289423580.html', 'file_21.docx', 'Учебный процесс']</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -998,19 +998,19 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['https://www.hse.ru/studyspravka/plan', 'https://electives.hse', 'https://www.hse.ru/docs/490481113.html', 'https://www.hse.ru/studyspravka/kontr']</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>3</v>
       </c>
       <c r="N5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O5" t="n">
         <v>73</v>
       </c>
-      <c r="P5" t="n">
+      <c r="P5" t="b">
         <v>1</v>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1019,46 +1019,46 @@
         </is>
       </c>
       <c r="R5" t="n">
+        <v>9.437844</v>
+      </c>
+      <c r="S5" t="n">
         <v>8</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>69</v>
       </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
         <v>8.625</v>
       </c>
-      <c r="U5" t="n">
+      <c r="V5" t="n">
         <v>0.8115942028985508</v>
       </c>
-      <c r="V5" t="n">
+      <c r="W5" t="n">
         <v>0.7002854347229004</v>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>0.218845397233963</v>
       </c>
-      <c r="X5" t="n">
+      <c r="Y5" t="n">
         <v>0.08086920529603958</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>22.23612969715292</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="AA5" t="n">
         <v>0.5656224489212036</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AB5" t="n">
         <v>0.3846144080162048</v>
       </c>
-      <c r="AB5" t="n">
-        <v>0</v>
-      </c>
       <c r="AC5" t="n">
+        <v>0.03846153846153846</v>
+      </c>
+      <c r="AD5" t="n">
         <v>0.3417143523693085</v>
       </c>
-      <c r="AD5" t="b">
-        <v>1</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>9.437844</v>
+      <c r="AE5" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['https://www.hse.ru/studyspravka/lms', 'file_9.docx', 'Учебный процесс', 'Цифровые системы', 'https://www.hse.ru/studyspravka/step', 'file_555.docx', 'Деньги', 'Учебный процесс', 'Цифровые системы', 'https://www.hse.ru/evaluation/students_structure', 'file_508.docx', 'Практическая подготовка', 'Цифровые системы', 'Обратная связь', 'https://www.hse.ru/studyspravka/kursovrab', 'file_275.docx', 'Деньги', 'Учебный процесс', 'Практическая подготовка', 'Траектории обучения', 'Перемещения студентов / Изменения статусов студентов', 'Цифровые системы', 'Наука']</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1117,19 +1117,19 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['https://www.hse.ru/studyspravka/lms', 'https://www.hse.ru/studyspravka/step', 'https://www.hse.ru/evaluation/students_structure', 'https://www.hse.ru/studyspravka/kursovrab']</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>8</v>
       </c>
       <c r="N6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O6" t="n">
         <v>63</v>
       </c>
-      <c r="P6" t="n">
+      <c r="P6" t="b">
         <v>1</v>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1138,46 +1138,46 @@
         </is>
       </c>
       <c r="R6" t="n">
+        <v>12.788267</v>
+      </c>
+      <c r="S6" t="n">
         <v>8</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>58</v>
       </c>
-      <c r="T6" t="n">
+      <c r="U6" t="n">
         <v>7.25</v>
       </c>
-      <c r="U6" t="n">
+      <c r="V6" t="n">
         <v>0.8620689655172413</v>
       </c>
-      <c r="V6" t="n">
+      <c r="W6" t="n">
         <v>0.5816411375999451</v>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>0.3026489317417145</v>
       </c>
-      <c r="X6" t="n">
+      <c r="Y6" t="n">
         <v>0.1157098859548569</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>18.94528557621851</v>
       </c>
-      <c r="Z6" t="n">
+      <c r="AA6" t="n">
         <v>0.568882167339325</v>
       </c>
-      <c r="AA6" t="n">
+      <c r="AB6" t="n">
         <v>0.524564802646637</v>
       </c>
-      <c r="AB6" t="n">
+      <c r="AC6" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.3308235108852386</v>
+      </c>
+      <c r="AE6" t="b">
         <v>0</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0.3308235108852386</v>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>12.788267</v>
       </c>
     </row>
     <row r="7">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['https://www.hse.ru/evaluation/students_mission', 'file_510.docx', 'Учебный процесс', 'Цифровые системы', 'Обратная связь', 'https://www.hse.ru/studyspravka/new_regulations', 'file_367.docx', 'Деньги', 'Учебный процесс', 'Практическая подготовка', 'ГИА', 'Траектории обучения', 'Цифровые компетенции', 'Перемещения студентов / Изменения статусов студентов', 'https://www.hse.ru/studyspravka/vks', 'file_198.docx', 'Учебный процесс', 'Цифровые системы', 'Обратная связь', 'https://www.hse.ru/dataculture/dc_courses', 'file_2.docx', 'Учебный процесс', 'Траектории обучения', 'Цифровые компетенции']</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1236,19 +1236,19 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['https://www.hse.ru/evaluation/students_mission', 'https://www.hse.ru/studyspravka/new_regulations', 'https://www.hse.ru/studyspravka/vks', 'https://www.hse.ru/dataculture/dc_courses']</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>4</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O7" t="n">
         <v>50</v>
       </c>
-      <c r="P7" t="n">
+      <c r="P7" t="b">
         <v>1</v>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1257,46 +1257,46 @@
         </is>
       </c>
       <c r="R7" t="n">
+        <v>16.902959</v>
+      </c>
+      <c r="S7" t="n">
         <v>7</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>43</v>
       </c>
-      <c r="T7" t="n">
+      <c r="U7" t="n">
         <v>6.142857142857143</v>
       </c>
-      <c r="U7" t="n">
+      <c r="V7" t="n">
         <v>0.9767441860465116</v>
       </c>
-      <c r="V7" t="n">
+      <c r="W7" t="n">
         <v>0.2970072627067566</v>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>0.6198377013206482</v>
       </c>
-      <c r="X7" t="n">
+      <c r="Y7" t="n">
         <v>0.08315511047840118</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>14.65227638656207</v>
       </c>
-      <c r="Z7" t="n">
+      <c r="AA7" t="n">
         <v>0.5120701789855957</v>
       </c>
-      <c r="AA7" t="n">
+      <c r="AB7" t="n">
         <v>0.3483472466468811</v>
       </c>
-      <c r="AB7" t="n">
+      <c r="AC7" t="n">
+        <v>0.05882352941176471</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.3166845142841339</v>
+      </c>
+      <c r="AE7" t="b">
         <v>0</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0.3166845142841339</v>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>16.902959</v>
       </c>
     </row>
     <row r="8">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['https://www.hse.ru/studyspravka/plan', 'file_254.docx', 'Деньги', 'Учебный процесс', 'Практическая подготовка', 'Траектории обучения', 'Английский язык', 'Перемещения студентов / Изменения статусов студентов', 'Дополнительное образование', 'Социальные вопросы', 'https://www.hse.ru/studyspravka/kontr', 'file_270.docx', 'Деньги', 'Учебный процесс', 'Перемещения студентов / Изменения статусов студентов', 'https://www.hse.ru/docs/552116522.html', 'file_20.docx', 'Учебный процесс', 'https://www.hse.ru/docs/480101460.html', 'file_75.docx', 'Учебный процесс', 'Траектории обучения', 'Перемещения студентов / Изменения статусов студентов']</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1355,19 +1355,19 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['https://www.hse.ru/studyspravka/plan', 'https://www.hse.ru/studyspravka/kontr', 'https://www.hse.ru/docs/552116522.html', 'https://www.hse.ru/docs/480101460.html']</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>3</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O8" t="n">
         <v>68</v>
       </c>
-      <c r="P8" t="n">
+      <c r="P8" t="b">
         <v>1</v>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1376,46 +1376,46 @@
         </is>
       </c>
       <c r="R8" t="n">
+        <v>22.491718</v>
+      </c>
+      <c r="S8" t="n">
         <v>4</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>63</v>
       </c>
-      <c r="T8" t="n">
+      <c r="U8" t="n">
         <v>15.75</v>
       </c>
-      <c r="U8" t="n">
+      <c r="V8" t="n">
         <v>0.9206349206349206</v>
       </c>
-      <c r="V8" t="n">
+      <c r="W8" t="n">
         <v>0.8035047650337219</v>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>0.09150311350822449</v>
       </c>
-      <c r="X8" t="n">
+      <c r="Y8" t="n">
         <v>0.1049920693039894</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>26.14820319284076</v>
       </c>
-      <c r="Z8" t="n">
+      <c r="AA8" t="n">
         <v>0.613169252872467</v>
       </c>
-      <c r="AA8" t="n">
+      <c r="AB8" t="n">
         <v>0.3778668940067291</v>
       </c>
-      <c r="AB8" t="n">
-        <v>0</v>
-      </c>
       <c r="AC8" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AD8" t="n">
         <v>0.4061979651451111</v>
       </c>
-      <c r="AD8" t="b">
-        <v>1</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>22.491718</v>
+      <c r="AE8" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['https://www.hse.ru/studyspravka/plan', 'file_254.docx', 'Деньги', 'Учебный процесс', 'Практическая подготовка', 'Траектории обучения', 'Английский язык', 'Перемещения студентов / Изменения статусов студентов', 'Дополнительное образование', 'Социальные вопросы', 'https://www.hse.ru/studyspravka/kontr', 'file_270.docx', 'Деньги', 'Учебный процесс', 'Перемещения студентов / Изменения статусов студентов', 'https://www.hse.ru/docs/552116522.html', 'file_20.docx', 'Учебный процесс', 'https://www.hse.ru/docs/480101460.html', 'file_75.docx', 'Учебный процесс', 'Траектории обучения', 'Перемещения студентов / Изменения статусов студентов']</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1474,19 +1474,19 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['https://www.hse.ru/studyspravka/plan', 'https://www.hse.ru/studyspravka/kontr', 'https://www.hse.ru/docs/552116522.html', 'https://www.hse.ru/docs/480101460.html']</t>
         </is>
       </c>
       <c r="M9" t="n">
         <v>3</v>
       </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O9" t="n">
         <v>79</v>
       </c>
-      <c r="P9" t="n">
+      <c r="P9" t="b">
         <v>1</v>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1495,46 +1495,46 @@
         </is>
       </c>
       <c r="R9" t="n">
+        <v>6.643707</v>
+      </c>
+      <c r="S9" t="n">
         <v>5</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>71</v>
       </c>
-      <c r="T9" t="n">
+      <c r="U9" t="n">
         <v>14.2</v>
       </c>
-      <c r="U9" t="n">
+      <c r="V9" t="n">
         <v>0.8732394366197183</v>
       </c>
-      <c r="V9" t="n">
+      <c r="W9" t="n">
         <v>0.8526800870895386</v>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>0.08085054904222488</v>
       </c>
-      <c r="X9" t="n">
+      <c r="Y9" t="n">
         <v>0.06646936386823654</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>32.99265792104332</v>
       </c>
-      <c r="Z9" t="n">
+      <c r="AA9" t="n">
         <v>0.6415992379188538</v>
       </c>
-      <c r="AA9" t="n">
+      <c r="AB9" t="n">
         <v>0.3645102977752686</v>
       </c>
-      <c r="AB9" t="n">
-        <v>0</v>
-      </c>
       <c r="AC9" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AD9" t="n">
         <v>0.3971919417381287</v>
       </c>
-      <c r="AD9" t="b">
-        <v>1</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>6.643707</v>
+      <c r="AE9" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['https://www.hse.ru/org/hse/elective_courses/MN_OI', 'file_280.docx', 'Учебный процесс', 'Траектории обучения', 'https://electives.hse.ru/', 'file_193.docx', 'Деньги', 'Учебный процесс', 'Практическая подготовка', 'ГИА', 'Траектории обучения', 'Английский язык', 'Цифровые компетенции', 'Онлайн-обучение', 'Дополнительное образование', 'https://www.hse.ru/docs/289423580.html', 'file_21.docx', 'Учебный процесс', 'https://www.hse.ru/docs/490481113.html', 'file_26.docx', 'Учебный процесс', 'Траектории обучения']</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1593,19 +1593,19 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['https://www.hse.ru/org/hse/elective_courses/MN_OI', 'https://electives.hse', 'https://www.hse.ru/docs/289423580.html', 'https://www.hse.ru/docs/490481113.html']</t>
         </is>
       </c>
       <c r="M10" t="n">
         <v>3</v>
       </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O10" t="n">
         <v>92</v>
       </c>
-      <c r="P10" t="n">
+      <c r="P10" t="b">
         <v>1</v>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1614,46 +1614,46 @@
         </is>
       </c>
       <c r="R10" t="n">
+        <v>19.871674</v>
+      </c>
+      <c r="S10" t="n">
         <v>5</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>85</v>
       </c>
-      <c r="T10" t="n">
+      <c r="U10" t="n">
         <v>17</v>
       </c>
-      <c r="U10" t="n">
+      <c r="V10" t="n">
         <v>0.8823529411764706</v>
       </c>
-      <c r="V10" t="n">
+      <c r="W10" t="n">
         <v>0.4402622878551483</v>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>0.150562509894371</v>
       </c>
-      <c r="X10" t="n">
+      <c r="Y10" t="n">
         <v>0.4091752171516418</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>28.8386335466637</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="AA10" t="n">
         <v>0.5793296694755554</v>
       </c>
-      <c r="AA10" t="n">
+      <c r="AB10" t="n">
         <v>0.308877021074295</v>
       </c>
-      <c r="AB10" t="n">
-        <v>0</v>
-      </c>
       <c r="AC10" t="n">
+        <v>0.05882352941176471</v>
+      </c>
+      <c r="AD10" t="n">
         <v>0.3485716581344604</v>
       </c>
-      <c r="AD10" t="b">
-        <v>1</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>19.871674</v>
+      <c r="AE10" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['https://www.hse.ru/dataculture/faq', 'file_7.docx', 'Учебный процесс', 'Траектории обучения', 'Цифровые компетенции', 'https://www.hse.ru/docs/941289807.html', 'file_119.docx', 'Деньги', 'Учебный процесс', 'Перемещения студентов / Изменения статусов студентов', 'Социальные вопросы', 'https://www.hse.ru/studyspravka/instpaliat', 'file_257.docx', 'Учебный процесс', 'Практическая подготовка', 'ГИА', 'Перемещения студентов / Изменения статусов студентов', 'Цифровые системы', 'https://www.hse.ru/docs/480101460.html', 'file_75.docx', 'Учебный процесс', 'Траектории обучения', 'Перемещения студентов / Изменения статусов студентов']</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1705,22 +1705,26 @@
       <c r="J11" t="n">
         <v>0</v>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cleaned context is empty, getting info from page contents in contexts: </t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['https://www.hse.ru/dataculture/faq', 'https://www.hse.ru/docs/941289807.html', 'https://www.hse.ru/studyspravka/instpaliat', 'https://www.hse.ru/docs/480101460.html']</t>
         </is>
       </c>
       <c r="M11" t="n">
         <v>7</v>
       </c>
       <c r="N11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O11" t="n">
         <v>37</v>
       </c>
-      <c r="P11" t="n">
+      <c r="P11" t="b">
         <v>1</v>
       </c>
       <c r="Q11" t="inlineStr">
@@ -1729,46 +1733,46 @@
         </is>
       </c>
       <c r="R11" t="n">
+        <v>5.582061</v>
+      </c>
+      <c r="S11" t="n">
         <v>2</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>33</v>
       </c>
-      <c r="T11" t="n">
+      <c r="U11" t="n">
         <v>16.5</v>
       </c>
-      <c r="U11" t="n">
+      <c r="V11" t="n">
         <v>0.9393939393939394</v>
       </c>
-      <c r="V11" t="n">
-        <v>0.0591357909142971</v>
-      </c>
       <c r="W11" t="n">
-        <v>0.7407082915306091</v>
+        <v>0.1329716742038727</v>
       </c>
       <c r="X11" t="n">
-        <v>0.2001559287309647</v>
+        <v>0.802874743938446</v>
       </c>
       <c r="Y11" t="n">
+        <v>0.06415354460477829</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.86798102949914</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.3796107172966003</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.4682086408138275</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.05882352941176471</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.4082683324813843</v>
+      </c>
+      <c r="AE11" t="b">
         <v>0</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>0.05906565114855766</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>0.4682086408138275</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>0.4082683324813843</v>
-      </c>
-      <c r="AD11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>5.582061</v>
       </c>
     </row>
     <row r="12">
@@ -1809,7 +1813,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['https://www.hse.ru/studyspravka/indexam', 'file_342.docx', 'Учебный процесс', 'Английский язык', 'https://www.hse.ru/studyspravka/indexam', 'file_342.docx', 'Учебный процесс', 'Английский язык', 'https://www.hse.ru/docs/981357423.html', 'file_33.docx', 'Учебный процесс', 'Траектории обучения', 'Английский язык', 'Перемещения студентов / Изменения статусов студентов', 'Дополнительное образование', 'https://www.hse.ru/docs/981357423.html', 'file_33.docx', 'Учебный процесс', 'Траектории обучения', 'Английский язык', 'Перемещения студентов / Изменения статусов студентов', 'Дополнительное образование', 'https://www.hse.ru/studyspravka/perezach', 'file_244.docx', 'Учебный процесс', 'Английский язык', 'https://www.hse.ru/studyspravka/perezach', 'file_244.docx', 'Учебный процесс', 'Английский язык']</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1820,22 +1824,26 @@
       <c r="J12" t="n">
         <v>0</v>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Cleaned context is empty, getting info from page contents in contexts: Независимый экзамен по английскому языку Вся актуальная информация об экзамене представлена на странице Центра независимой экспертизы по английскому языку Независимый экзамен по английскому языку Экзамен нацелен на проверку уровня владения английским языком и является обязательным для всех студентов бакалавриата и специалитета, кроме студентов очно-заочной формы обучения. Основной период сдачи НЭ С 4 модуля 2 курса по 3 модуль 3 курса. Возможна также сдача на более раннем периоде обучения — на 1 курсе или в 1-3 модулях 2 курса. НЭ по английскому языку Независимый экзамен по английскому языку Вся актуальная информация об экзамене представлена на странице Центра независимой экспертизы по английскому языку Независимый экзамен по английскому языку Экзамен нацелен на проверку уровня владения английским языком и является обязательным для всех студентов бакалавриата и специалитета, кроме студентов очно-заочной формы обучения. Основной период сдачи НЭ С 4 модуля 2 курса по 3 модуль 3 курса. Во</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['https://www.hse.ru/studyspravka/indexam', 'https://www.hse.ru/studyspravka/indexam', 'https://www.hse.ru/docs/981357423.html', 'https://www.hse.ru/docs/981357423.html', 'https://www.hse.ru/studyspravka/perezach', 'https://www.hse.ru/studyspravka/perezach', 'https://www.ets.org/toefl/institutions/ibt/about/how.html]', 'https://ielts.org/take-a-test/test-', 'http://www.cambridgeenglish.org/exams-and-tests/business-', 'http://www.cambridgeenglish.org/exams-and-tests/business-vantage/]', 'http://www.cambridgeenglish.org/exams/advanced/]', 'http://www.cambridgeenglish.org/exams/proficiency/]']</t>
         </is>
       </c>
       <c r="M12" t="n">
         <v>5</v>
       </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O12" t="n">
         <v>134</v>
       </c>
-      <c r="P12" t="n">
+      <c r="P12" t="b">
         <v>1</v>
       </c>
       <c r="Q12" t="inlineStr">
@@ -1844,46 +1852,46 @@
         </is>
       </c>
       <c r="R12" t="n">
+        <v>75.47844499999999</v>
+      </c>
+      <c r="S12" t="n">
         <v>10</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>128</v>
       </c>
-      <c r="T12" t="n">
+      <c r="U12" t="n">
         <v>12.8</v>
       </c>
-      <c r="U12" t="n">
+      <c r="V12" t="n">
         <v>0.828125</v>
       </c>
-      <c r="V12" t="n">
-        <v>0.2264359444379807</v>
-      </c>
       <c r="W12" t="n">
-        <v>0.7399323582649231</v>
+        <v>0.9536458849906921</v>
       </c>
       <c r="X12" t="n">
-        <v>0.03363167867064476</v>
+        <v>0.03059844858944416</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>0.01575563102960587</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.009722703136503696</v>
+        <v>34.37434889468366</v>
       </c>
       <c r="AA12" t="n">
+        <v>0.6364415884017944</v>
+      </c>
+      <c r="AB12" t="n">
         <v>0.4295795261859894</v>
       </c>
-      <c r="AB12" t="n">
-        <v>0</v>
-      </c>
       <c r="AC12" t="n">
+        <v>0.09090909090909091</v>
+      </c>
+      <c r="AD12" t="n">
         <v>0.3264357149600983</v>
       </c>
-      <c r="AD12" t="b">
-        <v>1</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>75.47844499999999</v>
+      <c r="AE12" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1924,7 +1932,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['https://www.hse.ru/docs/578704961.html', 'file_68.docx', 'Учебный процесс', 'Перемещения студентов / Изменения статусов студентов', 'https://www.hse.ru/docs/578704961.html', 'file_68.docx', 'Учебный процесс', 'Перемещения студентов / Изменения статусов студентов', 'https://www.hse.ru/docs/594887310.html', 'file_51.docx', 'Учебный процесс', 'Практическая подготовка', 'ГИА', 'Перемещения студентов / Изменения статусов студентов', 'https://www.hse.ru/docs/594887310.html', 'file_51.docx', 'Учебный процесс', 'Практическая подготовка', 'ГИА', 'Перемещения студентов / Изменения статусов студентов', 'https://www.hse.ru/docs/552116522.html', 'file_20.docx', 'Учебный процесс', 'https://www.hse.ru/docs/552116522.html', 'file_20.docx', 'Учебный процесс']</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1935,22 +1943,26 @@
       <c r="J13" t="n">
         <v>0</v>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Cleaned context is empty, getting info from page contents in contexts: Декан факультета – руководитель факультета, в том числе в филиале, или руководитель ассоциированного с факультетом подразделения (школы, института, кафедры). Приложение к приказу НИУ ВШЭ от 22.03.2022 № 6.18.1-01/220322-6 УТВЕРЖДЕНЫ ученым советом НИУ ВШЭ протокол от 25.02.2022 № 02 Правила  перевода студентов бакалавриата, специалитета, магистратуры  Национального исследовательского университета «Высшая школа экономики» и студентов бакалавриата, специалитета, магистратуры других образовательных организаций в Национальный исследовательский университет «Высшая школа экономики» Москва, 2022 Используемые понятия и сокращения Правила – Правила перевода студентов бакалавриата, специалитета, магистратуры Национального исследовательского университета «Высшая школа экономики» и студентов бакалавриата, специалитета, магистратуры других образовательных организаций в Национальный исследовательский университет «Высшая школа экономики». НИУ ВШЭ, Университет – Национальный исследовательский универси</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['https://www.hse.ru/docs/578704961.html', 'https://www.hse.ru/docs/578704961.html', 'https://www.hse.ru/docs/594887310.html', 'https://www.hse.ru/docs/594887310.html', 'https://www.hse.ru/docs/552116522.html', 'https://www.hse.ru/docs/552116522.html']</t>
         </is>
       </c>
       <c r="M13" t="n">
         <v>3</v>
       </c>
       <c r="N13" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O13" t="n">
         <v>48</v>
       </c>
-      <c r="P13" t="n">
+      <c r="P13" t="b">
         <v>0</v>
       </c>
       <c r="Q13" t="inlineStr">
@@ -1959,46 +1971,46 @@
         </is>
       </c>
       <c r="R13" t="n">
+        <v>11.438174</v>
+      </c>
+      <c r="S13" t="n">
         <v>3</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>47</v>
       </c>
-      <c r="T13" t="n">
+      <c r="U13" t="n">
         <v>15.66666666666667</v>
       </c>
-      <c r="U13" t="n">
+      <c r="V13" t="n">
         <v>0.9361702127659575</v>
       </c>
-      <c r="V13" t="n">
-        <v>0.2270500808954239</v>
-      </c>
       <c r="W13" t="n">
-        <v>0.7659614086151123</v>
+        <v>0.3689203560352325</v>
       </c>
       <c r="X13" t="n">
-        <v>0.006988511886447668</v>
+        <v>0.5908573269844055</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>0.04022230580449104</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.04002891480922699</v>
+        <v>21.19742004626498</v>
       </c>
       <c r="AA13" t="n">
+        <v>0.5865079760551453</v>
+      </c>
+      <c r="AB13" t="n">
         <v>0.3319467902183533</v>
       </c>
-      <c r="AB13" t="n">
-        <v>0</v>
-      </c>
       <c r="AC13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AD13" t="n">
         <v>0.3266102075576782</v>
       </c>
-      <c r="AD13" t="b">
-        <v>1</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>11.438174</v>
+      <c r="AE13" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -2039,7 +2051,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['https://www.hse.ru/docs/594887310.html', 'file_51.docx', 'Учебный процесс', 'Практическая подготовка', 'ГИА', 'Перемещения студентов / Изменения статусов студентов', 'https://www.hse.ru/docs/594887310.html', 'file_51.docx', 'Учебный процесс', 'Практическая подготовка', 'ГИА', 'Перемещения студентов / Изменения статусов студентов', 'https://www.hse.ru/docs/578704961.html', 'file_68.docx', 'Учебный процесс', 'Перемещения студентов / Изменения статусов студентов', 'https://www.hse.ru/docs/578704961.html', 'file_68.docx', 'Учебный процесс', 'Перемещения студентов / Изменения статусов студентов', 'https://www.hse.ru/docs/229339407.html', 'file_55.docx', 'Учебный процесс', 'ГИА', 'https://www.hse.ru/docs/229339407.html', 'file_55.docx', 'Учебный процесс', 'ГИА']</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2050,22 +2062,26 @@
       <c r="J14" t="n">
         <v>0</v>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Cleaned context is empty, getting info from page contents in contexts: Менеджер программы – руководитель учебного офиса образовательной программы или менеджер, в функции которого входит сопровождение процессов, связанных с обучением студентов образовательной программы. Приложение  к приказу НИУ ВШЭ от 20.04.2022 № 6.18.1-01/200422-7 УТВЕРЖДЕНО ученым советом НИУ ВШЭ протокол от 25.03.2022 № 03 Положение об организации и проведении государственной итоговой аттестации студентов образовательных программ высшего образования – программ бакалавриата, специалитета и магистратуры Национального исследовательского университета «Высшая школа экономики» Используемые понятия и сокращения Положение – Положение об организации и проведении государственной итоговой аттестации студентов образовательных программ высшего образования – программ бакалавриата, специалитета и магистратуры Национального исследовательского университета «Высшая школа экономики».  НИУ ВШЭ – Национальный исследовательский университет «Высшая школа экономики». ГИА – государственная итоговая аттестация</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['https://www.hse.ru/docs/594887310.html', 'https://www.hse.ru/docs/594887310.html', 'https://www.hse.ru/docs/578704961.html', 'https://www.hse.ru/docs/578704961.html', 'https://www.hse.ru/docs/229339407.html', 'https://www.hse.ru/docs/229339407.html']</t>
         </is>
       </c>
       <c r="M14" t="n">
         <v>4</v>
       </c>
       <c r="N14" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O14" t="n">
         <v>43</v>
       </c>
-      <c r="P14" t="n">
+      <c r="P14" t="b">
         <v>0</v>
       </c>
       <c r="Q14" t="inlineStr">
@@ -2074,46 +2090,46 @@
         </is>
       </c>
       <c r="R14" t="n">
+        <v>11.061041</v>
+      </c>
+      <c r="S14" t="n">
         <v>3</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>42</v>
       </c>
-      <c r="T14" t="n">
+      <c r="U14" t="n">
         <v>14</v>
       </c>
-      <c r="U14" t="n">
+      <c r="V14" t="n">
         <v>0.8809523809523809</v>
       </c>
-      <c r="V14" t="n">
-        <v>0.1757386028766632</v>
-      </c>
       <c r="W14" t="n">
-        <v>0.8179226517677307</v>
+        <v>0.8635555505752563</v>
       </c>
       <c r="X14" t="n">
-        <v>0.006338721141219139</v>
+        <v>0.09277147054672241</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>0.04367303848266602</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.0575280599296093</v>
+        <v>26.99094547417145</v>
       </c>
       <c r="AA14" t="n">
+        <v>0.6204245686531067</v>
+      </c>
+      <c r="AB14" t="n">
         <v>0.4146169424057007</v>
       </c>
-      <c r="AB14" t="n">
-        <v>0</v>
-      </c>
       <c r="AC14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AD14" t="n">
         <v>0.3761751651763916</v>
       </c>
-      <c r="AD14" t="b">
-        <v>1</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>11.061041</v>
+      <c r="AE14" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -2154,7 +2170,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['https://www.hse.ru/docs/896351333.html', 'file_63.docx', 'Деньги', 'Учебный процесс', 'ГИА', 'Английский язык', 'Цифровые компетенции', 'Перемещения студентов / Изменения статусов студентов', 'Социальные вопросы', 'ВУЦ', 'https://www.hse.ru/docs/896351333.html', 'file_63.docx', 'Деньги', 'Учебный процесс', 'ГИА', 'Английский язык', 'Цифровые компетенции', 'Перемещения студентов / Изменения статусов студентов', 'Социальные вопросы', 'ВУЦ', 'https://www.hse.ru/docs/802687500.html', 'file_47.docx', 'Учебный процесс', 'ВУЦ', 'https://www.hse.ru/docs/802687500.html', 'file_47.docx', 'Учебный процесс', 'ВУЦ']</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2165,22 +2181,26 @@
       <c r="J15" t="n">
         <v>1</v>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Cleaned context is empty, getting info from page contents in contexts: 6.2. При отчислении по обстоятельствам, не зависящим от воли сторон отчисление осуществляется в случае:         Приложение         к приказу НИУ ВШЭ         от 13.02.2024 № 6.18-01/130224-5      УТВЕРЖДЕНЫ ученым советом НИУ ВШЭ (протокол от 31.01.2024 № 02) ПОРЯДОК И ОСНОВАНИЯ  отчисления обучающихся из Национального исследовательского университета «Высшая школа экономики» 1. Общие положения 1.1. Порядок и основания отчисления обучающихся из Национального исследовательского университета «Высшая школа экономики» (далее соответственно – Порядок, НИУ ВШЭ или университет) устанавливают основания для отчисления и общие требования к процедуре прекращения образовательных отношений. 1.2. Особенности порядка отчисления отдельных категорий обучающихся могут быть установлены отдельными локальными нормативными актами университета. 1.3. При досрочном прекращении образовательных отношений между обучающимся и НИУ ВШЭ в трехдневный срок после издания приказа об отчислении, лицу, отчисленному из НИУ В</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['https://www.hse.ru/docs/896351333.html', 'https://www.hse.ru/docs/896351333.html', 'https://www.hse.ru/docs/802687500.html', 'https://www.hse.ru/docs/802687500.html']</t>
         </is>
       </c>
       <c r="M15" t="n">
         <v>8</v>
       </c>
       <c r="N15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O15" t="n">
         <v>99</v>
       </c>
-      <c r="P15" t="n">
+      <c r="P15" t="b">
         <v>1</v>
       </c>
       <c r="Q15" t="inlineStr">
@@ -2189,46 +2209,46 @@
         </is>
       </c>
       <c r="R15" t="n">
+        <v>15.01742</v>
+      </c>
+      <c r="S15" t="n">
         <v>8</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>98</v>
       </c>
-      <c r="T15" t="n">
+      <c r="U15" t="n">
         <v>12.25</v>
       </c>
-      <c r="U15" t="n">
+      <c r="V15" t="n">
         <v>0.8571428571428571</v>
       </c>
-      <c r="V15" t="n">
-        <v>0.3169826865196228</v>
-      </c>
       <c r="W15" t="n">
-        <v>0.6322436332702637</v>
+        <v>0.5956088900566101</v>
       </c>
       <c r="X15" t="n">
-        <v>0.05077367275953293</v>
+        <v>0.2985297739505768</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>0.1058612987399101</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.02268198505043983</v>
+        <v>23.73566013812404</v>
       </c>
       <c r="AA15" t="n">
+        <v>0.5864739418029785</v>
+      </c>
+      <c r="AB15" t="n">
         <v>0.4444022476673126</v>
       </c>
-      <c r="AB15" t="n">
-        <v>0</v>
-      </c>
       <c r="AC15" t="n">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="AD15" t="n">
         <v>0.07933842390775681</v>
       </c>
-      <c r="AD15" t="b">
-        <v>1</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>15.01742</v>
+      <c r="AE15" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -2269,7 +2289,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['https://www.hse.ru/studyspravka/indexam', 'file_342.docx', 'Учебный процесс', 'Английский язык', 'https://www.hse.ru/studyspravka/indexam', 'file_342.docx', 'Учебный процесс', 'Английский язык', 'https://www.hse.ru/docs/981357423.html', 'file_33.docx', 'Учебный процесс', 'Траектории обучения', 'Английский язык', 'Перемещения студентов / Изменения статусов студентов', 'Дополнительное образование', 'https://www.hse.ru/docs/981357423.html', 'file_33.docx', 'Учебный процесс', 'Траектории обучения', 'Английский язык', 'Перемещения студентов / Изменения статусов студентов', 'Дополнительное образование', 'https://www.hse.ru/studyspravka/perezach', 'file_244.docx', 'Учебный процесс', 'Английский язык', 'https://www.hse.ru/studyspravka/perezach', 'file_244.docx', 'Учебный процесс', 'Английский язык']</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2287,19 +2307,19 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['https://www.hse.ru/studyspravka/indexam', 'https://www.hse.ru/studyspravka/indexam', 'https://www.hse.ru/docs/981357423.html', 'https://www.hse.ru/docs/981357423.html', 'https://www.hse.ru/studyspravka/perezach', 'https://www.hse.ru/studyspravka/perezach', 'https://www.ets.org/toefl/institutions/ibt/about/how.html]', 'https://ielts.org/take-a-test/test-', 'http://www.cambridgeenglish.org/exams-and-tests/business-', 'http://www.cambridgeenglish.org/exams-and-tests/business-vantage/]', 'http://www.cambridgeenglish.org/exams/advanced/]', 'http://www.cambridgeenglish.org/exams/proficiency/]']</t>
         </is>
       </c>
       <c r="M16" t="n">
         <v>5</v>
       </c>
       <c r="N16" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O16" t="n">
         <v>103</v>
       </c>
-      <c r="P16" t="n">
+      <c r="P16" t="b">
         <v>1</v>
       </c>
       <c r="Q16" t="inlineStr">
@@ -2308,46 +2328,46 @@
         </is>
       </c>
       <c r="R16" t="n">
+        <v>76.455904</v>
+      </c>
+      <c r="S16" t="n">
         <v>10</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>100</v>
       </c>
-      <c r="T16" t="n">
+      <c r="U16" t="n">
         <v>10</v>
       </c>
-      <c r="U16" t="n">
+      <c r="V16" t="n">
         <v>0.83</v>
       </c>
-      <c r="V16" t="n">
+      <c r="W16" t="n">
         <v>0.8105148077011108</v>
       </c>
-      <c r="W16" t="n">
+      <c r="X16" t="n">
         <v>0.1482192575931549</v>
       </c>
-      <c r="X16" t="n">
+      <c r="Y16" t="n">
         <v>0.04126590490341187</v>
       </c>
-      <c r="Y16" t="n">
+      <c r="Z16" t="n">
         <v>39.41558650841488</v>
       </c>
-      <c r="Z16" t="n">
+      <c r="AA16" t="n">
         <v>0.6877592206001282</v>
       </c>
-      <c r="AA16" t="n">
+      <c r="AB16" t="n">
         <v>0.4140537679195404</v>
       </c>
-      <c r="AB16" t="n">
-        <v>0</v>
-      </c>
       <c r="AC16" t="n">
+        <v>0.09090909090909091</v>
+      </c>
+      <c r="AD16" t="n">
         <v>0.3441203832626343</v>
       </c>
-      <c r="AD16" t="b">
-        <v>1</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>76.455904</v>
+      <c r="AE16" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -2388,7 +2408,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['https://www.hse.ru/docs/981357423.html', 'file_33.docx', 'Учебный процесс', 'Траектории обучения', 'Английский язык', 'Перемещения студентов / Изменения статусов студентов', 'Дополнительное образование', 'https://www.hse.ru/docs/981357423.html', 'file_33.docx', 'Учебный процесс', 'Траектории обучения', 'Английский язык', 'Перемещения студентов / Изменения статусов студентов', 'Дополнительное образование', 'https://www.hse.ru/studyspravka/indexam', 'file_342.docx', 'Учебный процесс', 'Английский язык', 'https://www.hse.ru/studyspravka/indexam', 'file_342.docx', 'Учебный процесс', 'Английский язык', 'https://www.hse.ru/docs/1043432520.html', 'file_29.docx', 'Деньги', 'Учебный процесс', 'Практическая подготовка', 'https://www.hse.ru/docs/1043432520.html', 'file_29.docx', 'Деньги', 'Учебный процесс', 'Практическая подготовка']</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2406,19 +2426,19 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['https://www.hse.ru/docs/981357423.html', 'https://www.hse.ru/docs/981357423.html', 'https://www.hse.ru/studyspravka/indexam', 'https://www.hse.ru/studyspravka/indexam', 'https://www.hse.ru/docs/1043432520.html', 'https://www.hse.ru/docs/1043432520.html']</t>
         </is>
       </c>
       <c r="M17" t="n">
         <v>4</v>
       </c>
       <c r="N17" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O17" t="n">
         <v>116</v>
       </c>
-      <c r="P17" t="n">
+      <c r="P17" t="b">
         <v>1</v>
       </c>
       <c r="Q17" t="inlineStr">
@@ -2427,46 +2447,46 @@
         </is>
       </c>
       <c r="R17" t="n">
+        <v>69.76844699999999</v>
+      </c>
+      <c r="S17" t="n">
         <v>11</v>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
         <v>117</v>
       </c>
-      <c r="T17" t="n">
+      <c r="U17" t="n">
         <v>10.63636363636364</v>
       </c>
-      <c r="U17" t="n">
+      <c r="V17" t="n">
         <v>0.8205128205128205</v>
       </c>
-      <c r="V17" t="n">
+      <c r="W17" t="n">
         <v>0.02551595121622086</v>
       </c>
-      <c r="W17" t="n">
+      <c r="X17" t="n">
         <v>0.0141816595569253</v>
       </c>
-      <c r="X17" t="n">
+      <c r="Y17" t="n">
         <v>0.9603023529052734</v>
       </c>
-      <c r="Y17" t="n">
+      <c r="Z17" t="n">
         <v>21.85423297472887</v>
       </c>
-      <c r="Z17" t="n">
+      <c r="AA17" t="n">
         <v>0.5572482347488403</v>
       </c>
-      <c r="AA17" t="n">
+      <c r="AB17" t="n">
         <v>0.5388981103897095</v>
       </c>
-      <c r="AB17" t="n">
-        <v>0</v>
-      </c>
       <c r="AC17" t="n">
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="AD17" t="n">
         <v>0.407770574092865</v>
       </c>
-      <c r="AD17" t="b">
-        <v>1</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>69.76844699999999</v>
+      <c r="AE17" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -2507,7 +2527,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['https://www.hse.ru/studyspravka/Skidki', 'file_469.docx', 'Деньги', 'Учебный процесс', 'Социальные вопросы', 'https://www.hse.ru/studyspravka/Skidki', 'file_469.docx', 'Деньги', 'Учебный процесс', 'Социальные вопросы']</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2525,19 +2545,19 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['https://www.hse.ru/studyspravka/Skidki', 'https://www.hse.ru/studyspravka/Skidki', 'https://admissions.hse', 'https://admissions.hse']</t>
         </is>
       </c>
       <c r="M18" t="n">
         <v>20</v>
       </c>
       <c r="N18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O18" t="n">
         <v>75</v>
       </c>
-      <c r="P18" t="n">
+      <c r="P18" t="b">
         <v>1</v>
       </c>
       <c r="Q18" t="inlineStr">
@@ -2546,46 +2566,46 @@
         </is>
       </c>
       <c r="R18" t="n">
+        <v>40.69813</v>
+      </c>
+      <c r="S18" t="n">
         <v>7</v>
       </c>
-      <c r="S18" t="n">
+      <c r="T18" t="n">
         <v>71</v>
       </c>
-      <c r="T18" t="n">
+      <c r="U18" t="n">
         <v>10.14285714285714</v>
       </c>
-      <c r="U18" t="n">
+      <c r="V18" t="n">
         <v>0.8309859154929577</v>
       </c>
-      <c r="V18" t="n">
+      <c r="W18" t="n">
         <v>0.8117402195930481</v>
       </c>
-      <c r="W18" t="n">
+      <c r="X18" t="n">
         <v>0.1196868494153023</v>
       </c>
-      <c r="X18" t="n">
+      <c r="Y18" t="n">
         <v>0.06857291609048843</v>
       </c>
-      <c r="Y18" t="n">
+      <c r="Z18" t="n">
         <v>20.22542792199814</v>
       </c>
-      <c r="Z18" t="n">
+      <c r="AA18" t="n">
         <v>0.5709909200668335</v>
       </c>
-      <c r="AA18" t="n">
+      <c r="AB18" t="n">
         <v>0.4775540828704834</v>
       </c>
-      <c r="AB18" t="n">
-        <v>0</v>
-      </c>
       <c r="AC18" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AD18" t="n">
         <v>0.2399558275938034</v>
       </c>
-      <c r="AD18" t="b">
-        <v>1</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>40.69813</v>
+      <c r="AE18" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -2626,7 +2646,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['https://www.hse.ru/docs/941197025.html', 'file_121.docx', 'Деньги', 'Учебный процесс', 'Перемещения студентов / Изменения статусов студентов', 'Социальные вопросы', 'https://www.hse.ru/docs/941197025.html', 'file_121.docx', 'Деньги', 'Учебный процесс', 'Перемещения студентов / Изменения статусов студентов', 'Социальные вопросы', 'https://www.hse.ru/docs/807180592.html', 'file_117.docx', 'Деньги', 'Учебный процесс', 'https://www.hse.ru/docs/807180592.html', 'file_117.docx', 'Деньги', 'Учебный процесс']</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2644,19 +2664,19 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['https://www.hse.ru/docs/941197025.html', 'https://www.hse.ru/docs/941197025.html', 'https://www.hse.ru/docs/807180592.html', 'https://www.hse.ru/docs/807180592.html']</t>
         </is>
       </c>
       <c r="M19" t="n">
         <v>13</v>
       </c>
       <c r="N19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O19" t="n">
         <v>75</v>
       </c>
-      <c r="P19" t="n">
+      <c r="P19" t="b">
         <v>1</v>
       </c>
       <c r="Q19" t="inlineStr">
@@ -2665,46 +2685,46 @@
         </is>
       </c>
       <c r="R19" t="n">
+        <v>23.960496</v>
+      </c>
+      <c r="S19" t="n">
         <v>9</v>
       </c>
-      <c r="S19" t="n">
+      <c r="T19" t="n">
         <v>73</v>
       </c>
-      <c r="T19" t="n">
+      <c r="U19" t="n">
         <v>8.111111111111111</v>
       </c>
-      <c r="U19" t="n">
+      <c r="V19" t="n">
         <v>0.9315068493150684</v>
       </c>
-      <c r="V19" t="n">
+      <c r="W19" t="n">
         <v>0.7287003397941589</v>
       </c>
-      <c r="W19" t="n">
+      <c r="X19" t="n">
         <v>0.1993875950574875</v>
       </c>
-      <c r="X19" t="n">
+      <c r="Y19" t="n">
         <v>0.07191210985183716</v>
       </c>
-      <c r="Y19" t="n">
+      <c r="Z19" t="n">
         <v>18.49770865545586</v>
       </c>
-      <c r="Z19" t="n">
+      <c r="AA19" t="n">
         <v>0.5516259670257568</v>
       </c>
-      <c r="AA19" t="n">
+      <c r="AB19" t="n">
         <v>0.5642526745796204</v>
       </c>
-      <c r="AB19" t="n">
-        <v>0</v>
-      </c>
       <c r="AC19" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="AD19" t="n">
         <v>0.2505658268928528</v>
       </c>
-      <c r="AD19" t="b">
-        <v>1</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>23.960496</v>
+      <c r="AE19" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -2756,7 +2776,11 @@
       <c r="J20" t="n">
         <v>0</v>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cleaned context is empty, getting info from page contents in contexts: </t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2766,55 +2790,55 @@
         <v>38</v>
       </c>
       <c r="N20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>6</v>
       </c>
-      <c r="P20" t="n">
+      <c r="P20" t="b">
         <v>0</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="n">
-        <v>1</v>
+        <v>35.038818</v>
       </c>
       <c r="S20" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="T20" t="n">
         <v>6</v>
       </c>
       <c r="U20" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="V20" t="n">
-        <v>0.0116930715739727</v>
+        <v>1</v>
       </c>
       <c r="W20" t="n">
-        <v>0.9848887920379639</v>
+        <v>0.04569604992866516</v>
       </c>
       <c r="X20" t="n">
-        <v>0.003418135223910213</v>
+        <v>0.9337512254714966</v>
       </c>
       <c r="Y20" t="n">
+        <v>0.02055267803370953</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1.376907527616445</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0.5088806748390198</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.4208573400974274</v>
+      </c>
+      <c r="AC20" t="n">
         <v>0</v>
       </c>
-      <c r="Z20" t="n">
-        <v>0.09988703578710556</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>0.4208573400974274</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC20" t="n">
+      <c r="AD20" t="n">
         <v>0.4935205280780792</v>
       </c>
-      <c r="AD20" t="inlineStr"/>
-      <c r="AE20" t="n">
-        <v>35.038818</v>
-      </c>
+      <c r="AE20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2865,7 +2889,11 @@
       <c r="J21" t="n">
         <v>0</v>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cleaned context is empty, getting info from page contents in contexts: </t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2875,55 +2903,55 @@
         <v>12</v>
       </c>
       <c r="N21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>6</v>
       </c>
-      <c r="P21" t="n">
+      <c r="P21" t="b">
         <v>0</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>47.734612</v>
       </c>
       <c r="S21" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="T21" t="n">
         <v>6</v>
       </c>
       <c r="U21" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="V21" t="n">
-        <v>0.0116930715739727</v>
+        <v>1</v>
       </c>
       <c r="W21" t="n">
-        <v>0.9848887920379639</v>
+        <v>0.04569604992866516</v>
       </c>
       <c r="X21" t="n">
-        <v>0.003418135223910213</v>
+        <v>0.9337512254714966</v>
       </c>
       <c r="Y21" t="n">
+        <v>0.02055267803370953</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1.376907527616445</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0.5088806748390198</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.6003119945526123</v>
+      </c>
+      <c r="AC21" t="n">
         <v>0</v>
       </c>
-      <c r="Z21" t="n">
-        <v>0.09988703578710556</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>0.6003119945526123</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC21" t="n">
+      <c r="AD21" t="n">
         <v>0.6101843118667603</v>
       </c>
-      <c r="AD21" t="inlineStr"/>
-      <c r="AE21" t="n">
-        <v>47.734612</v>
-      </c>
+      <c r="AE21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/result.xlsx
+++ b/data/result.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE21"/>
+  <dimension ref="A1:AE36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -677,13 +677,13 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="W2" t="n">
-        <v>0.6118826866149902</v>
+        <v>0.6118837594985962</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1876140832901001</v>
+        <v>0.1876134872436523</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.2005032300949097</v>
+        <v>0.2005028128623962</v>
       </c>
       <c r="Z2" t="n">
         <v>29.3062528169179</v>
@@ -692,13 +692,13 @@
         <v>0.5740185379981995</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.3189123272895813</v>
+        <v>0.3189123570919037</v>
       </c>
       <c r="AC2" t="n">
         <v>0.05882352941176471</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.3276387453079224</v>
+        <v>0.3276387155056</v>
       </c>
       <c r="AE2" t="b">
         <v>1</v>
@@ -796,13 +796,13 @@
         <v>0.8787878787878788</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6489430069923401</v>
+        <v>0.648942232131958</v>
       </c>
       <c r="X3" t="n">
-        <v>0.1347694993019104</v>
+        <v>0.1347696930170059</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.2162874639034271</v>
+        <v>0.2162880897521973</v>
       </c>
       <c r="Z3" t="n">
         <v>27.46260354420096</v>
@@ -811,7 +811,7 @@
         <v>0.6110109686851501</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.3152807950973511</v>
+        <v>0.3152808547019958</v>
       </c>
       <c r="AC3" t="n">
         <v>0.0625</v>
@@ -915,13 +915,13 @@
         <v>0.8115942028985508</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7002854347229004</v>
+        <v>0.7002846002578735</v>
       </c>
       <c r="X4" t="n">
-        <v>0.218845397233963</v>
+        <v>0.2188459187746048</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.08086920529603958</v>
+        <v>0.08086943626403809</v>
       </c>
       <c r="Z4" t="n">
         <v>22.23612969715292</v>
@@ -930,13 +930,13 @@
         <v>0.5656224489212036</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.3846144080162048</v>
+        <v>0.3846142888069153</v>
       </c>
       <c r="AC4" t="n">
         <v>0.05882352941176471</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.3417143523693085</v>
+        <v>0.341714084148407</v>
       </c>
       <c r="AE4" t="b">
         <v>1</v>
@@ -1034,13 +1034,13 @@
         <v>0.8115942028985508</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7002854347229004</v>
+        <v>0.7002846002578735</v>
       </c>
       <c r="X5" t="n">
-        <v>0.218845397233963</v>
+        <v>0.2188459187746048</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.08086920529603958</v>
+        <v>0.08086943626403809</v>
       </c>
       <c r="Z5" t="n">
         <v>22.23612969715292</v>
@@ -1049,13 +1049,13 @@
         <v>0.5656224489212036</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.3846144080162048</v>
+        <v>0.3846142888069153</v>
       </c>
       <c r="AC5" t="n">
         <v>0.03846153846153846</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.3417143523693085</v>
+        <v>0.341714084148407</v>
       </c>
       <c r="AE5" t="b">
         <v>1</v>
@@ -1153,13 +1153,13 @@
         <v>0.8620689655172413</v>
       </c>
       <c r="W6" t="n">
-        <v>0.5816411375999451</v>
+        <v>0.5816399455070496</v>
       </c>
       <c r="X6" t="n">
-        <v>0.3026489317417145</v>
+        <v>0.3026500046253204</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.1157098859548569</v>
+        <v>0.1157100796699524</v>
       </c>
       <c r="Z6" t="n">
         <v>18.94528557621851</v>
@@ -1168,13 +1168,13 @@
         <v>0.568882167339325</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.524564802646637</v>
+        <v>0.5245647430419922</v>
       </c>
       <c r="AC6" t="n">
         <v>0.0625</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.3308235108852386</v>
+        <v>0.3308233618736267</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
@@ -1272,13 +1272,13 @@
         <v>0.9767441860465116</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2970072627067566</v>
+        <v>0.2970059812068939</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6198377013206482</v>
+        <v>0.6198388338088989</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.08315511047840118</v>
+        <v>0.08315518498420715</v>
       </c>
       <c r="Z7" t="n">
         <v>14.65227638656207</v>
@@ -1287,13 +1287,13 @@
         <v>0.5120701789855957</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.3483472466468811</v>
+        <v>0.3483471870422363</v>
       </c>
       <c r="AC7" t="n">
         <v>0.05882352941176471</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.3166845142841339</v>
+        <v>0.3166846036911011</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
@@ -1391,13 +1391,13 @@
         <v>0.9206349206349206</v>
       </c>
       <c r="W8" t="n">
-        <v>0.8035047650337219</v>
+        <v>0.8035048246383667</v>
       </c>
       <c r="X8" t="n">
-        <v>0.09150311350822449</v>
+        <v>0.09150321036577225</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.1049920693039894</v>
+        <v>0.1049919724464417</v>
       </c>
       <c r="Z8" t="n">
         <v>26.14820319284076</v>
@@ -1406,7 +1406,7 @@
         <v>0.613169252872467</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.3778668940067291</v>
+        <v>0.3778669238090515</v>
       </c>
       <c r="AC8" t="n">
         <v>0.0625</v>
@@ -1510,13 +1510,13 @@
         <v>0.8732394366197183</v>
       </c>
       <c r="W9" t="n">
-        <v>0.8526800870895386</v>
+        <v>0.8526799082756042</v>
       </c>
       <c r="X9" t="n">
-        <v>0.08085054904222488</v>
+        <v>0.08085066080093384</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.06646936386823654</v>
+        <v>0.06646940857172012</v>
       </c>
       <c r="Z9" t="n">
         <v>32.99265792104332</v>
@@ -1525,13 +1525,13 @@
         <v>0.6415992379188538</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.3645102977752686</v>
+        <v>0.3645104765892029</v>
       </c>
       <c r="AC9" t="n">
         <v>0.0625</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.3971919417381287</v>
+        <v>0.3971920013427734</v>
       </c>
       <c r="AE9" t="b">
         <v>1</v>
@@ -1629,13 +1629,13 @@
         <v>0.8823529411764706</v>
       </c>
       <c r="W10" t="n">
-        <v>0.4402622878551483</v>
+        <v>0.440262109041214</v>
       </c>
       <c r="X10" t="n">
-        <v>0.150562509894371</v>
+        <v>0.1505621522665024</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.4091752171516418</v>
+        <v>0.4091757237911224</v>
       </c>
       <c r="Z10" t="n">
         <v>28.8386335466637</v>
@@ -1644,13 +1644,13 @@
         <v>0.5793296694755554</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.308877021074295</v>
+        <v>0.3088769316673279</v>
       </c>
       <c r="AC10" t="n">
         <v>0.05882352941176471</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.3485716581344604</v>
+        <v>0.3485714197158813</v>
       </c>
       <c r="AE10" t="b">
         <v>1</v>
@@ -1748,13 +1748,13 @@
         <v>0.9393939393939394</v>
       </c>
       <c r="W11" t="n">
-        <v>0.1329716742038727</v>
+        <v>0.1329706162214279</v>
       </c>
       <c r="X11" t="n">
-        <v>0.802874743938446</v>
+        <v>0.8028761148452759</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.06415354460477829</v>
+        <v>0.06415324658155441</v>
       </c>
       <c r="Z11" t="n">
         <v>2.86798102949914</v>
@@ -1763,13 +1763,13 @@
         <v>0.3796107172966003</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.4682086408138275</v>
+        <v>0.4682087302207947</v>
       </c>
       <c r="AC11" t="n">
         <v>0.05882352941176471</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.4082683324813843</v>
+        <v>0.4082682728767395</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
@@ -1867,28 +1867,28 @@
         <v>0.828125</v>
       </c>
       <c r="W12" t="n">
-        <v>0.9536458849906921</v>
+        <v>0.9536462426185608</v>
       </c>
       <c r="X12" t="n">
-        <v>0.03059844858944416</v>
+        <v>0.03059824556112289</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.01575563102960587</v>
+        <v>0.01575553975999355</v>
       </c>
       <c r="Z12" t="n">
         <v>34.37434889468366</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.6364415884017944</v>
+        <v>0.6364416480064392</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.4295795261859894</v>
+        <v>0.4295794069766998</v>
       </c>
       <c r="AC12" t="n">
         <v>0.09090909090909091</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.3264357149600983</v>
+        <v>0.3264356255531311</v>
       </c>
       <c r="AE12" t="b">
         <v>1</v>
@@ -1986,13 +1986,13 @@
         <v>0.9361702127659575</v>
       </c>
       <c r="W13" t="n">
-        <v>0.3689203560352325</v>
+        <v>0.3689208924770355</v>
       </c>
       <c r="X13" t="n">
-        <v>0.5908573269844055</v>
+        <v>0.590856671333313</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.04022230580449104</v>
+        <v>0.04022243618965149</v>
       </c>
       <c r="Z13" t="n">
         <v>21.19742004626498</v>
@@ -2001,13 +2001,13 @@
         <v>0.5865079760551453</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.3319467902183533</v>
+        <v>0.3319469392299652</v>
       </c>
       <c r="AC13" t="n">
         <v>0.1</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.3266102075576782</v>
+        <v>0.3266102373600006</v>
       </c>
       <c r="AE13" t="b">
         <v>1</v>
@@ -2105,13 +2105,13 @@
         <v>0.8809523809523809</v>
       </c>
       <c r="W14" t="n">
-        <v>0.8635555505752563</v>
+        <v>0.8635556697845459</v>
       </c>
       <c r="X14" t="n">
-        <v>0.09277147054672241</v>
+        <v>0.09277134388685226</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.04367303848266602</v>
+        <v>0.04367295652627945</v>
       </c>
       <c r="Z14" t="n">
         <v>26.99094547417145</v>
@@ -2120,13 +2120,13 @@
         <v>0.6204245686531067</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.4146169424057007</v>
+        <v>0.4146168828010559</v>
       </c>
       <c r="AC14" t="n">
         <v>0.1</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.3761751651763916</v>
+        <v>0.3761751055717468</v>
       </c>
       <c r="AE14" t="b">
         <v>1</v>
@@ -2224,13 +2224,13 @@
         <v>0.8571428571428571</v>
       </c>
       <c r="W15" t="n">
-        <v>0.5956088900566101</v>
+        <v>0.5956092476844788</v>
       </c>
       <c r="X15" t="n">
-        <v>0.2985297739505768</v>
+        <v>0.2985295951366425</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.1058612987399101</v>
+        <v>0.1058612614870071</v>
       </c>
       <c r="Z15" t="n">
         <v>23.73566013812404</v>
@@ -2239,13 +2239,13 @@
         <v>0.5864739418029785</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.4444022476673126</v>
+        <v>0.4444023370742798</v>
       </c>
       <c r="AC15" t="n">
         <v>0.08333333333333333</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.07933842390775681</v>
+        <v>0.07933861017227173</v>
       </c>
       <c r="AE15" t="b">
         <v>1</v>
@@ -2343,13 +2343,13 @@
         <v>0.83</v>
       </c>
       <c r="W16" t="n">
-        <v>0.8105148077011108</v>
+        <v>0.8105150461196899</v>
       </c>
       <c r="X16" t="n">
-        <v>0.1482192575931549</v>
+        <v>0.1482189893722534</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.04126590490341187</v>
+        <v>0.04126591980457306</v>
       </c>
       <c r="Z16" t="n">
         <v>39.41558650841488</v>
@@ -2358,13 +2358,13 @@
         <v>0.6877592206001282</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.4140537679195404</v>
+        <v>0.4140534698963165</v>
       </c>
       <c r="AC16" t="n">
         <v>0.09090909090909091</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.3441203832626343</v>
+        <v>0.3441202640533447</v>
       </c>
       <c r="AE16" t="b">
         <v>1</v>
@@ -2462,13 +2462,13 @@
         <v>0.8205128205128205</v>
       </c>
       <c r="W17" t="n">
-        <v>0.02551595121622086</v>
+        <v>0.02551578544080257</v>
       </c>
       <c r="X17" t="n">
-        <v>0.0141816595569253</v>
+        <v>0.0141815822571516</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.9603023529052734</v>
+        <v>0.9603025913238525</v>
       </c>
       <c r="Z17" t="n">
         <v>21.85423297472887</v>
@@ -2477,13 +2477,13 @@
         <v>0.5572482347488403</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.5388981103897095</v>
+        <v>0.538898229598999</v>
       </c>
       <c r="AC17" t="n">
         <v>0.07692307692307693</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.407770574092865</v>
+        <v>0.4077707231044769</v>
       </c>
       <c r="AE17" t="b">
         <v>1</v>
@@ -2581,13 +2581,13 @@
         <v>0.8309859154929577</v>
       </c>
       <c r="W18" t="n">
-        <v>0.8117402195930481</v>
+        <v>0.8117399215698242</v>
       </c>
       <c r="X18" t="n">
-        <v>0.1196868494153023</v>
+        <v>0.1196869239211082</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.06857291609048843</v>
+        <v>0.06857313215732574</v>
       </c>
       <c r="Z18" t="n">
         <v>20.22542792199814</v>
@@ -2596,13 +2596,13 @@
         <v>0.5709909200668335</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.4775540828704834</v>
+        <v>0.4775541126728058</v>
       </c>
       <c r="AC18" t="n">
         <v>0.2</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.2399558275938034</v>
+        <v>0.2399558573961258</v>
       </c>
       <c r="AE18" t="b">
         <v>1</v>
@@ -2700,28 +2700,28 @@
         <v>0.9315068493150684</v>
       </c>
       <c r="W19" t="n">
-        <v>0.7287003397941589</v>
+        <v>0.7287002205848694</v>
       </c>
       <c r="X19" t="n">
-        <v>0.1993875950574875</v>
+        <v>0.1993877440690994</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.07191210985183716</v>
+        <v>0.07191209495067596</v>
       </c>
       <c r="Z19" t="n">
         <v>18.49770865545586</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.5516259670257568</v>
+        <v>0.5516260266304016</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.5642526745796204</v>
+        <v>0.5642527341842651</v>
       </c>
       <c r="AC19" t="n">
         <v>0.125</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.2505658268928528</v>
+        <v>0.2505658864974976</v>
       </c>
       <c r="AE19" t="b">
         <v>1</v>
@@ -2815,13 +2815,13 @@
         <v>1</v>
       </c>
       <c r="W20" t="n">
-        <v>0.04569604992866516</v>
+        <v>0.04569605737924576</v>
       </c>
       <c r="X20" t="n">
-        <v>0.9337512254714966</v>
+        <v>0.9337513446807861</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.02055267803370953</v>
+        <v>0.02055264078080654</v>
       </c>
       <c r="Z20" t="n">
         <v>1.376907527616445</v>
@@ -2830,13 +2830,13 @@
         <v>0.5088806748390198</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.4208573400974274</v>
+        <v>0.4208574593067169</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.4935205280780792</v>
+        <v>0.4935205578804016</v>
       </c>
       <c r="AE20" t="inlineStr"/>
     </row>
@@ -2928,13 +2928,13 @@
         <v>1</v>
       </c>
       <c r="W21" t="n">
-        <v>0.04569604992866516</v>
+        <v>0.04569605737924576</v>
       </c>
       <c r="X21" t="n">
-        <v>0.9337512254714966</v>
+        <v>0.9337513446807861</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.02055267803370953</v>
+        <v>0.02055264078080654</v>
       </c>
       <c r="Z21" t="n">
         <v>1.376907527616445</v>
@@ -2943,15 +2943,1788 @@
         <v>0.5088806748390198</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.6003119945526123</v>
+        <v>0.6003120541572571</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.6101843118667603</v>
+        <v>0.610184371471405</v>
       </c>
       <c r="AE21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Студент</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Нижний Новгород</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Бакалавриат</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Цифровые системы</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>как мне попасть в смарт лмс</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>['Нижний Новгород', 'бакалавриат']</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>['Цифровые системы']</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>['https://electives.hse.ru/sw', 'file_256.docx', 'Деньги', 'Учебный процесс', 'Траектории обучения', 'Английский язык', 'Цифровые системы', 'https://electives.hse.ru/sw', 'file_256.docx', 'Деньги', 'Учебный процесс', 'Траектории обучения', 'Английский язык', 'Цифровые системы']</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Для входа в SmartWay LMS: 1. Перейдите по ссылке: [https://smartway.hse.ru](https://smartway.hse.ru) 2. Авторизуйтесь, используя данные корпоративной электронной почты (@edu.hse.ru). 3. После входа вы сможете работать с учебным планом, выбирать дисциплины и расписание в соответствии с графиком кампаний. Для корректной работы рекомендуется использовать компьютер. Подробные инструкции по выбору дисциплин доступны в разделе "Мой учебный план" системы. При возникновении технических проблем с доступом обращайтесь в учебный офис вашей образовательной программы.  Подробнее: https://electives.hse.ru/sw</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Инструкция по выбору курсов в SmartWay Инструкция для студента по работе в SmartWay Кампания выбора дисциплин на 2 семестр 2024/2025 учебный год состоит из двух волн: 1 волна - выбор дисциплин. Подача заявок на дисциплины с началом в 2-4 учебных модулях с отбором и без отбора. 2 волна - выбор расписания к дисциплинам + дополнительный выбор дисциплин с оставшимися местами, но обязательно сразу с расписанием. Нормативный объем обучения за учебный год - 60 кредитов (см. поле "Всего кредитов"). В текущей кампании предлагаются только дисциплины только первого семестра. Вход в сервис для выбора курсов SmartWay https://smartway.hse.ru Система открывается со стартом кампании Для корректной работы в системе используйте компьютер (выбор на маленьком экране расписания дисциплины с большим количеством учебных групп - крайне неудобный процесс) Коротко о важном: Заявки на дисциплины без отбора обрабатываются до 30 минут (при одновременной подаче большого количества заявок, в остальных случаях 1-5 ми</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>['https://electives.hse', 'https://smartway.hse', 'https://electives.hse', 'https://smartway.hse', 'https://smartway.hse', 'https://ruz.hse']</t>
+        </is>
+      </c>
+      <c r="M22" t="n">
+        <v>6</v>
+      </c>
+      <c r="N22" t="n">
+        <v>2</v>
+      </c>
+      <c r="O22" t="n">
+        <v>69</v>
+      </c>
+      <c r="P22" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>Предоставленные контексты содержат прямые инструкции по входу в систему SmartWay (Smart LMS). В Content 1 чётко указана ссылка для входа (https://smartway.hse.ru) и метод аутентификации через корпоративную почту. Дополнительные контексты подтверждают, что система используется для выбора дисциплин и расписания, что соответствует назначению LMS. Отрывки также содержат график кампаний и технические детали работы с интерфейсом, что подтверждает релевантность информации.</t>
+        </is>
+      </c>
+      <c r="R22" t="n">
+        <v>10.592411</v>
+      </c>
+      <c r="S22" t="n">
+        <v>11</v>
+      </c>
+      <c r="T22" t="n">
+        <v>69</v>
+      </c>
+      <c r="U22" t="n">
+        <v>6.272727272727272</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0.8695652173913043</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0.305145263671875</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0.6234638094902039</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0.07139087468385696</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>27.06718717736025</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0.6314249634742737</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.281583309173584</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0.2950622141361237</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Студент</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Нижний Новгород</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Бакалавриат</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Цифровые системы</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>как мне попасть в смарт лмс</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>['Нижний Новгород', 'бакалавриат']</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>['Цифровые системы']</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>['https://electives.hse.ru/sw', 'file_256.docx', 'Деньги', 'Учебный процесс', 'Траектории обучения', 'Английский язык', 'Цифровые системы', 'https://electives.hse.ru/sw', 'file_256.docx', 'Деньги', 'Учебный процесс', 'Траектории обучения', 'Английский язык', 'Цифровые системы', 'https://electives.hse.ru/sw', 'file_256.docx', 'Деньги', 'Учебный процесс', 'Траектории обучения', 'Английский язык', 'Цифровые системы', 'https://electives.hse.ru/sw', 'file_256.docx', 'Деньги', 'Учебный процесс', 'Траектории обучения', 'Английский язык', 'Цифровые системы']</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Для входа в SmartWay LMS: 1. Перейдите по ссылке: [https://smartway.hse.ru](https://smartway.hse.ru) 2. Авторизуйтесь, используя данные корпоративной электронной почты (@edu.hse.ru). 3. После входа вы сможете работать с учебным планом, выбирать дисциплины и расписание в соответствии с графиком кампаний. Для корректной работы рекомендуется использовать компьютер. Подробные инструкции по выбору дисциплин доступны в разделе "Мой учебный план" системы. При возникновении технических проблем с доступом обращайтесь в учебный офис вашей образовательной программы.  Подробнее: https://electives.hse.ru/sw</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Инструкция по выбору курсов в SmartWay Инструкция для студента по работе в SmartWay Кампания выбора дисциплин на 2 семестр 2024/2025 учебный год состоит из двух волн: 1 волна - выбор дисциплин. Подача заявок на дисциплины с началом в 2-4 учебных модулях с отбором и без отбора. 2 волна - выбор расписания к дисциплинам + дополнительный выбор дисциплин с оставшимися местами, но обязательно сразу с расписанием. Нормативный объем обучения за учебный год - 60 кредитов (см. поле "Всего кредитов"). В текущей кампании предлагаются только дисциплины только первого семестра. Вход в сервис для выбора курсов SmartWay https://smartway.hse.ru Система открывается со стартом кампании Для корректной работы в системе используйте компьютер (выбор на маленьком экране расписания дисциплины с большим количеством учебных групп - крайне неудобный процесс) Коротко о важном: Заявки на дисциплины без отбора обрабатываются до 30 минут (при одновременной подаче большого количества заявок, в остальных случаях 1-5 ми</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>['https://electives.hse', 'https://smartway.hse', 'https://electives.hse', 'https://smartway.hse', 'https://smartway.hse', 'https://ruz.hse']</t>
+        </is>
+      </c>
+      <c r="M23" t="n">
+        <v>6</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2</v>
+      </c>
+      <c r="O23" t="n">
+        <v>69</v>
+      </c>
+      <c r="P23" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>В предоставленных контекстах четко указан алгоритм входа в SmartWay: 1. Ссылка для входа: https://smartway.hse.ru 2. Авторизация через корпоративную почту (@edu.hse.ru) с использованием данных ЕЛК ВШЭ. 3. Для студентов требуется выбор типа учетной записи "Студенты". Дополнительно упомянуты технические аспекты (использование компьютера для удобства) и возможность восстановления пароля через учебный офис.</t>
+        </is>
+      </c>
+      <c r="R23" t="n">
+        <v>14.701391</v>
+      </c>
+      <c r="S23" t="n">
+        <v>11</v>
+      </c>
+      <c r="T23" t="n">
+        <v>69</v>
+      </c>
+      <c r="U23" t="n">
+        <v>6.272727272727272</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0.8695652173913043</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0.305145263671875</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0.6234638094902039</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0.07139087468385696</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>27.06718717736025</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0.6314249634742737</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0.281583309173584</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.2950622141361237</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Студент</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Нижний Новгород</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Бакалавриат</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Цифровые системы</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>что такое SmartLMS</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>['Нижний Новгород', 'бакалавриат']</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>['Цифровые системы']</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>['https://www.hse.ru/studyspravka/step', 'file_555.docx', 'Деньги', 'Учебный процесс', 'Цифровые системы', 'https://www.hse.ru/studyspravka/step', 'file_555.docx', 'Деньги', 'Учебный процесс', 'Цифровые системы']</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>В текущих документах НИУ ВШЭ информация о "SmartLMS" отсутствует. Возможно, имеется в виду стандартная система LMS (Learning Management System) университета или отдельный модуль "Электронное портфолио студента (СтЭП)". Для уточнения рекомендую обратиться в Службу поддержки LMS по электронной почте lms@hse.ru или в учебный офис вашей образовательной программы.  Подробнее: https://www.hse.ru/studyspravka/step</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Электронное портфолио студента Электронное портфолио студента НИУ ВШЭ В НИУ ВШЭ на базе on-line системы обучения Learning Management System (LMS) разработан сервис «Электронное портфолио студента (СтЭП)», который доступен в LMS после предварительной авторизации и разработан на русском и английском языках. СтЭП позволяет зафиксировать достижения студентов по следующим видам деятельности: учебная; научная; практики и проектная; культурно-творческая; общественная; спортивная; дополнительное образование. В рамках учебной деятельности бóльшая часть информации автоматически интегрируется в портфолио студента из учетной системы НИУ ВШЭ: информация об успеваемости студента, выполненные курсовые и выпускные квалификационные работы, исходящая мобильность внутри страны или на международном уровне с указанием изученных дисциплин. Здесь же дополнительно производится расчет текущего показателя GPA (Grade Point Average), на основании которого определяется успеваемость студента во многих зарубежных ун</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>['https://www.hse.ru/studyspravka/step', 'https://www.hse.ru/studyspravka/step']</t>
+        </is>
+      </c>
+      <c r="M24" t="n">
+        <v>3</v>
+      </c>
+      <c r="N24" t="n">
+        <v>2</v>
+      </c>
+      <c r="O24" t="n">
+        <v>48</v>
+      </c>
+      <c r="P24" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>В предоставленных отрывках отсутствует прямое упоминание термина "SmartLMS". Контексты описывают функционал электронного портфолио студента (СтЭП) в системе LMS НИУ ВШЭ, но не содержат информации о сервисах/модулях с таким названием. Возможная путаница терминов или устаревшее/альтернативное наименование части функционала LMS. Нет ни технических характеристик, ни интерфейсных особенностей, подтверждающих существование SmartLMS как отдельного продукта.</t>
+        </is>
+      </c>
+      <c r="R24" t="n">
+        <v>5.341155</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="n">
+        <v>49</v>
+      </c>
+      <c r="U24" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0.8775510204081632</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0.08514326810836792</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0.8211318254470825</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0.09372488409280777</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>22.05943450310278</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0.5986996293067932</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0.4088040590286255</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.3182565569877625</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Студент</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Нижний Новгород</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Бакалавриат</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Цифровые системы</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Как войти в SmartLms?</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>['Нижний Новгород', 'бакалавриат']</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>['Цифровые системы']</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>['https://electives.hse.ru/sw', 'file_256.docx', 'Деньги', 'Учебный процесс', 'Траектории обучения', 'Английский язык', 'Цифровые системы', 'https://electives.hse.ru/sw', 'file_256.docx', 'Деньги', 'Учебный процесс', 'Траектории обучения', 'Английский язык', 'Цифровые системы', 'https://electives.hse.ru/kpv', 'file_394.docx', 'Деньги', 'Учебный процесс', 'Траектории обучения', 'Английский язык', 'Цифровые системы', 'Дополнительное образование', 'https://electives.hse.ru/kpv', 'file_394.docx', 'Деньги', 'Учебный процесс', 'Траектории обучения', 'Английский язык', 'Цифровые системы', 'Дополнительное образование']</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Для входа в SmartLMS: 1. Перейдите по ссылке: https://lms.hse.ru. 2. Нажмите «Войти через ЕЛК ВШЭ». 3. Выберите тип учётной записи «Студенты». 4. Введите логин (корпоративную почту в домене @edu.hse.ru) и пароль. Если возникают технические проблемы, отключите VPN, попробуйте другой браузер (например, Google Chrome) или режим инкогнито. При ошибках авторизации обратитесь в [техподдержку ЕЛК ВШЭ](https://lk.hse.ru).  Подробнее: https://electives.hse.ru/sw</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Инструкция по выбору курсов в SmartWay Инструкция для студента по работе в SmartWay Кампания выбора дисциплин на 2 семестр 2024/2025 учебный год состоит из двух волн: 1 волна - выбор дисциплин. Подача заявок на дисциплины с началом в 2-4 учебных модулях с отбором и без отбора. 2 волна - выбор расписания к дисциплинам + дополнительный выбор дисциплин с оставшимися местами, но обязательно сразу с расписанием. Нормативный объем обучения за учебный год - 60 кредитов (см. поле "Всего кредитов"). В текущей кампании предлагаются только дисциплины только первого семестра. Вход в сервис для выбора курсов SmartWay https://smartway.hse.ru Система открывается со стартом кампании Для корректной работы в системе используйте компьютер (выбор на маленьком экране расписания дисциплины с большим количеством учебных групп - крайне неудобный процесс) Коротко о важном: Заявки на дисциплины без отбора обрабатываются до 30 минут (при одновременной подаче большого количества заявок, в остальных случаях 1-5 ми</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>['https://electives.hse', 'https://electives.hse', 'https://smartway.hse', 'https://smartway.hse', 'https://ruz.hse', 'https://electives.hse', 'https://electives.hse', 'https://smartway.hse']</t>
+        </is>
+      </c>
+      <c r="M25" t="n">
+        <v>4</v>
+      </c>
+      <c r="N25" t="n">
+        <v>4</v>
+      </c>
+      <c r="O25" t="n">
+        <v>56</v>
+      </c>
+      <c r="P25" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>В предоставленных контекстах присутствует детальная инструкция по входу в систему SmartWay через ЕЛК ВШЭ (выбор типа аккаунта, ввод корпоративной почты и пароля). Упоминание SmartLMS встречается в разделе с техническими рекомендациями, где указано, что вход в SmartLMS проходит через ту же авторизацию в ЕЛК ВШЭ. Это позволяет объединить процессы авторизации для SmartWay и SmartLMS.</t>
+        </is>
+      </c>
+      <c r="R25" t="n">
+        <v>28.274333</v>
+      </c>
+      <c r="S25" t="n">
+        <v>11</v>
+      </c>
+      <c r="T25" t="n">
+        <v>56</v>
+      </c>
+      <c r="U25" t="n">
+        <v>5.090909090909091</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0.9285714285714286</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0.3869276940822601</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0.4576513469219208</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0.1554209142923355</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>14.2108248219491</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0.5458833575248718</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0.4694782495498657</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.3024296760559082</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Студент</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Нижний Новгород</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Бакалавриат</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Цифровые системы</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Как работает LMS?</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>['Нижний Новгород', 'бакалавриат']</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>['Цифровые системы']</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Сервер не отвечает, пожалуйста, попробуйте позже.</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cleaned context is empty, getting info from page contents in contexts: </t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="M26" t="n">
+        <v>3</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>6</v>
+      </c>
+      <c r="P26" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="n">
+        <v>7.426901</v>
+      </c>
+      <c r="S26" t="n">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>6</v>
+      </c>
+      <c r="U26" t="n">
+        <v>6</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0.04569605737924576</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0.9337513446807861</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0.02055264078080654</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1.376907527616445</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0.5088806748390198</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0.466636061668396</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.4935205578804016</v>
+      </c>
+      <c r="AE26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Студент</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Нижний Новгород</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Бакалавриат</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Цифровые системы</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Как работает LMS?</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>['Нижний Новгород', 'бакалавриат']</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>['Цифровые системы']</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Сервер не отвечает, пожалуйста, попробуйте позже.</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cleaned context is empty, getting info from page contents in contexts: </t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="M27" t="n">
+        <v>3</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>6</v>
+      </c>
+      <c r="P27" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="n">
+        <v>5.487843</v>
+      </c>
+      <c r="S27" t="n">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>6</v>
+      </c>
+      <c r="U27" t="n">
+        <v>6</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0.04569605737924576</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0.9337513446807861</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0.02055264078080654</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1.376907527616445</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0.5088806748390198</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0.466636061668396</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.4935205578804016</v>
+      </c>
+      <c r="AE27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Студент</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Нижний Новгород</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Бакалавриат</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Цифровые системы</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Как работает LMS&gt;</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>['Нижний Новгород', 'бакалавриат']</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>['Цифровые системы']</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>['https://www.hse.ru/studyspravka/step', 'file_555.docx', 'Деньги', 'Учебный процесс', 'Цифровые системы', 'https://www.hse.ru/studyspravka/step', 'file_555.docx', 'Деньги', 'Учебный процесс', 'Цифровые системы']</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>LMS НИУ ВШЭ включает сервис «Электронное портфолио студента» (СтЭП), который автоматически фиксирует учебные достижения (успеваемость, GPA, курсовые работы) и позволяет вносить данные о научной, проектной, спортивной и другой деятельности с подтверждающими документами. Портфолио используется для подачи на повышенную стипендию и доступно сотрудникам вуза. Для уточнения других функций LMS (работа с курсами, заданиями и т.д.) обратитесь в Службу поддержки: lms@hse.ru. Подробнее о портфолио: https://lms.hse.ru/index.php?page=gradebook.  Подробнее: https://www.hse.ru/studyspravka/step</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Электронное портфолио студента Электронное портфолио студента НИУ ВШЭ В НИУ ВШЭ на базе on-line системы обучения Learning Management System (LMS) разработан сервис «Электронное портфолио студента (СтЭП)», который доступен в LMS после предварительной авторизации и разработан на русском и английском языках. СтЭП позволяет зафиксировать достижения студентов по следующим видам деятельности: учебная; научная; практики и проектная; культурно-творческая; общественная; спортивная; дополнительное образование. В рамках учебной деятельности бóльшая часть информации автоматически интегрируется в портфолио студента из учетной системы НИУ ВШЭ: информация об успеваемости студента, выполненные курсовые и выпускные квалификационные работы, исходящая мобильность внутри страны или на международном уровне с указанием изученных дисциплин. Здесь же дополнительно производится расчет текущего показателя GPA (Grade Point Average), на основании которого определяется успеваемость студента во многих зарубежных ун</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>['https://www.hse.ru/studyspravka/step', 'https://www.hse.ru/studyspravka/step']</t>
+        </is>
+      </c>
+      <c r="M28" t="n">
+        <v>3</v>
+      </c>
+      <c r="N28" t="n">
+        <v>2</v>
+      </c>
+      <c r="O28" t="n">
+        <v>65</v>
+      </c>
+      <c r="P28" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>В предоставленных контекстах LMS НИУ ВШЭ представлена как платформа, интегрирующая электронное портфолио студента (СтЭП). Описаны ключевые функции: автоматическая синхронизация данных об успеваемости, GPA, курсовых работах, мобильности, а также возможность самостоятельного добавления достижений в научной, проектной и внеучебной деятельности с подтверждающими документами. Указано, что портфолио используется для подачи на повышенную стипендию и доступно сотрудникам. Однако детали работы LMS как системы управления учебными курсами (например, доступ к материалам, заданиям, тестам) не раскрыты.</t>
+        </is>
+      </c>
+      <c r="R28" t="n">
+        <v>32.421433</v>
+      </c>
+      <c r="S28" t="n">
+        <v>7</v>
+      </c>
+      <c r="T28" t="n">
+        <v>66</v>
+      </c>
+      <c r="U28" t="n">
+        <v>9.428571428571429</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0.5848368406295776</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0.3667767941951752</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0.0483863577246666</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>27.87605973462894</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0.6445428133010864</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0.2388290017843246</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.3592509329319</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Студент</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Нижний Новгород</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Бакалавриат</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Цифровые системы</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Как работает LMS&gt;</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>['Нижний Новгород', 'бакалавриат']</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>['Цифровые системы']</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>['https://www.hse.ru/studyspravka/step', 'file_555.docx', 'Деньги', 'Учебный процесс', 'Цифровые системы', 'https://www.hse.ru/studyspravka/step', 'file_555.docx', 'Деньги', 'Учебный процесс', 'Цифровые системы']</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Learning Management System (LMS) НИУ ВШЭ обеспечивает: 1. **Электронное портфолио студентов** с автоматизированной интеграцией данных об успеваемости, курсовых работах и GPA из учётной системы вуза. 2. **Самостоятельное дополнение профиля** научными публикациями, проектами, практиками, спортивными и культурными достижениями с прикреплением подтверждающих документов. 3. **Подачу заявок на стипендии** на основе накопленных в системе достижений. 4. **Гибкие настройки приватности** — студенты сами определяют, какие разделы портфолио видны сотрудникам университета. Для технических вопросов и уточнений по функционалу LMS обращайтесь в службу поддержки: [lms@hse.ru](mailto:lms@hse.ru).  Подробнее: https://www.hse.ru/studyspravka/step</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Электронное портфолио студента Электронное портфолио студента НИУ ВШЭ В НИУ ВШЭ на базе on-line системы обучения Learning Management System (LMS) разработан сервис «Электронное портфолио студента (СтЭП)», который доступен в LMS после предварительной авторизации и разработан на русском и английском языках. СтЭП позволяет зафиксировать достижения студентов по следующим видам деятельности: учебная; научная; практики и проектная; культурно-творческая; общественная; спортивная; дополнительное образование. В рамках учебной деятельности бóльшая часть информации автоматически интегрируется в портфолио студента из учетной системы НИУ ВШЭ: информация об успеваемости студента, выполненные курсовые и выпускные квалификационные работы, исходящая мобильность внутри страны или на международном уровне с указанием изученных дисциплин. Здесь же дополнительно производится расчет текущего показателя GPA (Grade Point Average), на основании которого определяется успеваемость студента во многих зарубежных ун</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>['https://www.hse.ru/studyspravka/step', 'https://www.hse.ru/studyspravka/step']</t>
+        </is>
+      </c>
+      <c r="M29" t="n">
+        <v>3</v>
+      </c>
+      <c r="N29" t="n">
+        <v>2</v>
+      </c>
+      <c r="O29" t="n">
+        <v>81</v>
+      </c>
+      <c r="P29" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>Предоставленный контекст описывает ключевые аспекты работы LMS НИУ ВШЭ через сервис «Электронное портфолио студента (СтЭП)». В материалах детально раскрыто: - интеграция LMS с учётной системой университета для автоматического заполнения данных об успеваемости, курсовых работах, GPA; - функционал для самостоятельного добавления научных, проектных и внеучебных достижений с подтверждающими документами; - использование портфолио для подачи заявок на повышенные стипендии; - мультиязычный интерфейс (русский/английский) и дифференцированный доступ к данным (студенты контролируют видимость своих достижений). При этом общая архитектура LMS, интерфейс управления курсами или технические аспекты работы системы прямо не затрагиваются.</t>
+        </is>
+      </c>
+      <c r="R29" t="n">
+        <v>7.339773</v>
+      </c>
+      <c r="S29" t="n">
+        <v>12</v>
+      </c>
+      <c r="T29" t="n">
+        <v>85</v>
+      </c>
+      <c r="U29" t="n">
+        <v>7.083333333333333</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0.8705882352941177</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0.7335643172264099</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0.1938265115022659</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0.07260915637016296</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>30.43845356828178</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0.6184595227241516</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0.3082372844219208</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.3322506546974182</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Студент</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Магистратура</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Цифровые системы</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>как попасть в смарт лмс</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>['Москва', 'магистратура']</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>['Цифровые системы']</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>['https://www.hse.ru/studyspravka/practice', 'file_434.docx', 'Учебный процесс', 'Практическая подготовка', 'ГИА', 'Траектории обучения', 'Перемещения студентов / Изменения статусов студентов', 'Цифровые системы', 'Наука', 'https://www.hse.ru/studyspravka/practice', 'file_434.docx', 'Учебный процесс', 'Практическая подготовка', 'ГИА', 'Траектории обучения', 'Перемещения студентов / Изменения статусов студентов', 'Цифровые системы', 'Наука']</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Для доступа к системе Smart LMS (SmartPro): 1. Зайдите через [Единый личный кабинет студента](https://ulc.hse.ru/) с использованием стандартных логина и пароля НИУ ВШЭ. 2. Выберите раздел «Ярмарка Элементов практической подготовки» (SmartPro) для исследовательских/прикладных проектов. Для сервисных проектов используйте ["Ярмарку проектов" в LMS](https://lms.hse.ru/). Подробные инструкции: https://disk.yandex.ru/i/RDTivwZbf0mP4w  Подробнее: https://www.hse.ru/studyspravka/practice</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Практическая подготовка Практическая подготовка студентов НИУ ВШЭ Навигация страницы Основная информация Виды практической подготовки Отчетные документы Оценивание Академические задолженности Полезные ссылки Курсовая работа (КР) Выпускная квалификационная работа (ВКР) Ярмарка Элементов практической подготовки (SmartPro) Практическая подготовка — обязательная часть обучения на образовательной программе (ОП) бакалавриата, специалитета, и магистратуры. 1. Что такое практическая подготовка? Практическая подготовка — учебная активность, в ходе которой студенты приобретают практический опыт для своей будущей профессии. Практическая подготовка отличается от других видов учебной работы большей долей самостоятельной работы студента. Во время практической подготовки не бывает лекций или семинаров, но у студента есть возможность задавать вопросы и получать обратную связь у своего руководителя. 2. Как практическая подготовка реализуется в НИУ ВШЭ? Какие элементы практической подготовки включены в </t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>['https://www.hse.ru/studyspravka/practice', 'https://www.hse.ru/studyspravka/practice', 'https://www.hse.ru/data/2022/07/12/1620501633/%D0%98%D0%BD%D1%81%D1%82%D1%80%D1%83%D0%BA%D1%86%D0%B8%D1%8F%20%D0%BF%D0%BE%20%D1%80%D0%B0%D0%B1%D0%BE%D1%82%D0%B5%20%D1%81%20%C2%AB%D0%AF%D1%80%D0%BC%D0%B0%D1%80%D0%BA%D0%BE%D0%B9%20%D0%BF%D1%80%D0%BE%D0%B5%D0%BA%D1%82%D0%BE%D0%B2%C2%BB.pdf]', 'https://disk.yandex']</t>
+        </is>
+      </c>
+      <c r="M30" t="n">
+        <v>5</v>
+      </c>
+      <c r="N30" t="n">
+        <v>2</v>
+      </c>
+      <c r="O30" t="n">
+        <v>46</v>
+      </c>
+      <c r="P30" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>В предоставленных материалах объясняется, что доступ к SmartPro (сервису для элементов практической подготовки) осуществляется через Единый личный кабинет студента. - Content 14 указывает, что подача заявок на проекты осуществляется через SmartPro с использованием логина/пароля от Единого ЛК. - В Content 15 упоминается LMS как система для регистрации на сервисные проекты ("Ярмарка проектов"). - Указаны прямые инструкции по регистрации через оба сервиса с привязкой к учетным данным НИУ ВШЭ.</t>
+        </is>
+      </c>
+      <c r="R30" t="n">
+        <v>7.668459</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="n">
+        <v>45</v>
+      </c>
+      <c r="U30" t="n">
+        <v>9</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0.5980914235115051</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0.2990416586399078</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0.1028669029474258</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>16.96339627955849</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0.5493311882019043</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0.2395793795585632</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.2407440543174744</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Студент</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Магистратура</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Цифровые системы</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>что такое smart lms</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>['Москва', 'магистратура']</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>['Цифровые системы']</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>['https://www.hse.ru/studyspravka/start', 'file_365.docx', 'Деньги', 'Учебный процесс', 'Цифровые системы', 'Безопасность', 'Социальные вопросы', 'ВУЦ', 'https://www.hse.ru/studyspravka/start', 'file_365.docx', 'Деньги', 'Учебный процесс', 'Цифровые системы', 'Безопасность', 'Социальные вопросы', 'ВУЦ', 'https://www.hse.ru/studyspravka/start', 'file_365.docx', 'Деньги', 'Учебный процесс', 'Цифровые системы', 'Безопасность', 'Социальные вопросы', 'ВУЦ']</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>SmartLMS — это единая образовательная платформа НИУ ВШЭ, объединяющая студентов и преподавателей. В системе преподаватели размещают материалы курсов, задания и контрольные работы, а студенты загружают выполненные работы. Для входа используется логин в формате `login@edu.hse.ru` и пароль от корпоративной почты. SmartLMS является частью цифровой инфраструктуры университета наряду с РУЗ (системой расписания) и другими сервисами.  Подробнее: https://www.hse.ru/studyspravka/start</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Здесь расположена «выразительная кнопка», социальные и административные сервисы для студентов. А ещё в личном кабинете можно управлять своими подписками на анонсы мероприятий университета, чтобы быть в курсе последних событий. LMS — это единое образовательное пространство первого поколения. Каждый студент при входе в LMS попадает в свой личный кабинет, в котором он увидит список всех учебных дисциплин, которые назначены для изучения в соответствии с индивидуальным учебным планом. Здесь же находится электронная зачетная книжка.</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>['https://www.hse.ru/studyspravka/start', 'https://www.hse.ru/studyspravka/start', 'https://www.hse.ru/mirror/pubs/share/856720243.doc]', 'https://www.hse.ru/mirror/pubs/share/856720245.doc]', 'https://www.hse.ru/mirror/pubs/share/856720247.pdf]', 'https://vk.com/hselibrary]', 'https://t.me/s/hse_library/]', 'https://www.mos.ru/socialnaya-karta/services-proverka-grazhdanina-v-reestre-studentov/]', 'http://www.mos.ru/]', 'https://www.mos.ru/karta-moskvicha/services-proverka-sostojanija-izgotovlenija-karty-moskvicha/]', 'https://www.hse.ru/org/hse/ouk/mil/', 'https://ivisa.hse', 'https://www.hse.ru/studyspravka/start']</t>
+        </is>
+      </c>
+      <c r="M31" t="n">
+        <v>4</v>
+      </c>
+      <c r="N31" t="n">
+        <v>3</v>
+      </c>
+      <c r="O31" t="n">
+        <v>55</v>
+      </c>
+      <c r="P31" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>В предоставленных контекстах содержится четкое определение SmartLMS. В разделе "Цифровые сервисы НИУ ВШЭ" указано, что SmartLMS — это единое образовательное пространство, связывающее участников учебного процесса. Контент объясняет функционал системы: загрузка материалов преподавателями, выполнение заданий студентами, а также способ авторизации через корпоративную почту. Дополнительные упоминания в контенте подтверждают эту информацию без противоречий.</t>
+        </is>
+      </c>
+      <c r="R31" t="n">
+        <v>23.375678</v>
+      </c>
+      <c r="S31" t="n">
+        <v>7</v>
+      </c>
+      <c r="T31" t="n">
+        <v>56</v>
+      </c>
+      <c r="U31" t="n">
+        <v>8</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0.8928571428571429</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0.2229481488466263</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0.7493617534637451</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0.02769004739820957</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>23.52130053222877</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0.5905360579490662</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0.260980635881424</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.2774877548217773</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Студент</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Нижний Новгород</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Бакалавриат</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Цифровые системы</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Как работает LMS&gt;</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>['Нижний Новгород', 'бакалавриат']</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>['Цифровые системы']</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>['https://www.hse.ru/studyspravka/step', 'file_555.docx', 'Деньги', 'Учебный процесс', 'Цифровые системы', 'https://www.hse.ru/studyspravka/step', 'file_555.docx', 'Деньги', 'Учебный процесс', 'Цифровые системы']</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>LMS НИУ ВШЭ включает в себя сервис электронного портфолио (СтЭП), который позволяет студентам фиксировать академические достижения (автоматически из учетной системы), научные работы, практики, проекты, культурно-творческую активность и дополнительное образование (MOOC, курсы). Данные из портфолио используются для подачи заявок на стипендии. Часть информации доступна сотрудникам ВШЭ с учетом настроек видимости. Для общего понимания работы LMS (доступ к курсам, заданиям, оценкам и др.) рекомендуем обратиться в службу поддержки: lms@hse.ru.  Подробнее: https://www.hse.ru/studyspravka/step</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Электронное портфолио студента Электронное портфолио студента НИУ ВШЭ В НИУ ВШЭ на базе on-line системы обучения Learning Management System (LMS) разработан сервис «Электронное портфолио студента (СтЭП)», который доступен в LMS после предварительной авторизации и разработан на русском и английском языках. СтЭП позволяет зафиксировать достижения студентов по следующим видам деятельности: учебная; научная; практики и проектная; культурно-творческая; общественная; спортивная; дополнительное образование. В рамках учебной деятельности бóльшая часть информации автоматически интегрируется в портфолио студента из учетной системы НИУ ВШЭ: информация об успеваемости студента, выполненные курсовые и выпускные квалификационные работы, исходящая мобильность внутри страны или на международном уровне с указанием изученных дисциплин. Здесь же дополнительно производится расчет текущего показателя GPA (Grade Point Average), на основании которого определяется успеваемость студента во многих зарубежных ун</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>['https://www.hse.ru/studyspravka/step', 'https://www.hse.ru/studyspravka/step']</t>
+        </is>
+      </c>
+      <c r="M32" t="n">
+        <v>3</v>
+      </c>
+      <c r="N32" t="n">
+        <v>2</v>
+      </c>
+      <c r="O32" t="n">
+        <v>69</v>
+      </c>
+      <c r="P32" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>В предоставленном контенте детально описан функционал системы LMS через призму сервиса "Электронное портфолио студента (СтЭП)". - Content объясняет, что LMS служит платформой для фиксации учебных (автоматическая интеграция данных об успеваемости, GPA) и внеучебных достижений (наука, практики, проекты, спорт и др.). - Указано, что система поддерживает загрузку подтверждающих документов и частично синхронизирована с учетными данными университета. - Упомянуты элементы управления доступом к информации (студент выбирает, какие данные видны сотрудникам). - Приведены сведения о привязке портфолио к стипендиальным программам. Однако общий принцип работы LMS (регистрация, интерфейс, инструменты для преподавателей, интеграция с расписанием, системами тестирования и др.) не раскрыт.</t>
+        </is>
+      </c>
+      <c r="R32" t="n">
+        <v>25.217777</v>
+      </c>
+      <c r="S32" t="n">
+        <v>7</v>
+      </c>
+      <c r="T32" t="n">
+        <v>71</v>
+      </c>
+      <c r="U32" t="n">
+        <v>10.14285714285714</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0.8732394366197183</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0.5914051532745361</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0.3776390552520752</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0.03095579333603382</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>31.05179448556056</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0.652143657207489</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0.2542132139205933</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.3747718930244446</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Студент</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Нижний Новгород</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Бакалавриат</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Социальные вопросы</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>как сделать пропуск для машины?</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>['Нижний Новгород', 'бакалавриат']</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>['Социальные вопросы']</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>['https://www.hse.ru/docs/205851345.html', 'file_85.docx', 'Перемещения студентов / Изменения статусов студентов', 'Безопасность', 'Социальные вопросы', 'https://www.hse.ru/docs/205851345.html', 'file_85.docx', 'Перемещения студентов / Изменения статусов студентов', 'Безопасность', 'Социальные вопросы', 'https://www.hse.ru/docs/205851345.html', 'file_85.docx', 'Перемещения студентов / Изменения статусов студентов', 'Безопасность', 'Социальные вопросы', 'https://www.hse.ru/docs/205851345.html', 'file_85.docx', 'Перемещения студентов / Изменения статусов студентов', 'Безопасность', 'Социальные вопросы']</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Информация о порядке оформления пропуска для автомобиля в предоставленных документах отсутствует. Для уточнения обратитесь в Дирекцию по управлению общежитиями, гостиницами и учебно-оздоровительными комплексами (ДУОГУК) или в службу безопасности НИУ ВШЭ. Контакты можно найти в [Справочнике студента](https://www.hse.ru/studyspravka).  Подробнее: https://www.hse.ru/docs/205851345.html</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>6.1.20. передачи пропуска, обеспечивающего проход в здания Университета или в общежитие, другим лица, а также допуска по своему пропуску других лиц, путем самостоятельного многократного прикладывания ЭП к турникету;</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>['https://www.hse.ru/docs/205851345.html', 'https://www.hse.ru/docs/205851345.html', 'https://www.hse.ru/docs/205851345.html', 'https://www.hse.ru/docs/205851345.html']</t>
+        </is>
+      </c>
+      <c r="M33" t="n">
+        <v>5</v>
+      </c>
+      <c r="N33" t="n">
+        <v>4</v>
+      </c>
+      <c r="O33" t="n">
+        <v>38</v>
+      </c>
+      <c r="P33" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>В предоставленных отрывках Правил внутреннего распорядка студенческого общежития НИУ ВШЭ информация о пропусках для автомобилей отсутствует. - В пункте 3.3 упоминается пропуск только для выноса крупногабаритных вещей, который выдается администрацией общежития. - Основной контекст о пропусках (пункты 3.1, 9.9) касается электронных пропусков (ЭП) для прохода людей в здания. - Нет данных о парковках, въезде на территорию или оформлении автомобильных пропусков.</t>
+        </is>
+      </c>
+      <c r="R33" t="n">
+        <v>27.769536</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3</v>
+      </c>
+      <c r="T33" t="n">
+        <v>38</v>
+      </c>
+      <c r="U33" t="n">
+        <v>12.66666666666667</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0.8947368421052632</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0.1287773996591568</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0.8090506196022034</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0.06217197328805923</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>17.40638722006327</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0.4927469491958618</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0.3017936050891876</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.3169112801551819</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Студент</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Бакалавриат</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Обратная связь</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Анонимен ли СОП?</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>['Москва', 'бакалавриат']</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>['Обратная связь']</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>['https://www.hse.ru/evaluation/students_structure', 'file_508.docx', 'Практическая подготовка', 'Цифровые системы', 'Обратная связь', 'https://www.hse.ru/evaluation/students_structure', 'file_508.docx', 'Практическая подготовка', 'Цифровые системы', 'Обратная связь', 'https://www.hse.ru/evaluation', 'file_511.docx', 'Учебный процесс', 'Цифровые системы', 'Обратная связь', 'https://www.hse.ru/evaluation', 'file_511.docx', 'Учебный процесс', 'Цифровые системы', 'Обратная связь', 'https://www.hse.ru/docs/318993988.html', 'file_86.docx', 'Учебный процесс', 'Обратная связь', 'https://www.hse.ru/docs/318993988.html', 'file_86.docx', 'Учебный процесс', 'Обратная связь']</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Да, студенческая оценка преподавания (СОП) полностью анонимна. Никто не может узнать, какие конкретные оценки или комментарии оставил тот или иной студент. Данные обрабатываются в обобщенном виде, а текстовые отзывы очищаются от личной информации перед передачей преподавателям. Это позволяет обеспечить объективность и честность обратной связи.  Подробнее: https://www.hse.ru/evaluation/students\_structure</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>1</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Студенческая оценка преподавания (СОП) Анкета Структура и заполнение анкеты Принципы обратной связи в Вышке Дисциплины с промежуточной аттестацией: вопросы и советы по заполнению обратной связи Преподаватели по этим дисциплинам: вопросы и советы по заполнению обратной связи Онлайн-курсы: вопросы и советы по заполнению обратной связи Проекты: вопросы и советы по заполнению обратной связи Дисциплины с промежуточной аттестацией в будущих модулях: вопросы и советы по заполнению обратной связи Общая организация учебного процесса: вопросы и советы по заполнению обратной связи Из модуля «Обратная связь» по курсу БЖД Дисциплины с промежуточной аттестацией Вопросы по дисциплинам с промежуточной аттестацией Числовые оценки (от 1 до 5 + « затрудняюсь ответить » ): Полезность курса для расширения кругозора и разностороннего развития Новизна полученных знаний Сложность курса для успешного прохождения («1» — курс очень легкий, «5» — курс очень сложный для прохождения) Открытые вопросы (развернутый о</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>['https://www.hse.ru/evaluation/students_structure', 'https://www.hse.ru/evaluation/students_structure', 'https://www.hse.ru/evaluation', 'https://www.hse.ru/evaluation', 'https://www.hse.ru/mirror/pubs/share/328275958]', 'https://www.hse.ru/docs/318993988.html', 'https://www.hse.ru/docs/318993988.html']</t>
+        </is>
+      </c>
+      <c r="M34" t="n">
+        <v>3</v>
+      </c>
+      <c r="N34" t="n">
+        <v>6</v>
+      </c>
+      <c r="O34" t="n">
+        <v>46</v>
+      </c>
+      <c r="P34" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>В предоставленных контентах неоднократно подчеркивается анонимность СОП. Например: - В первом контенте прямо указано: "Да, СОП анонимен, поэтому никто не увидит, кому из студентов принадлежат какие-либо конкретные оценки или комментарии". - В разделе "Экосистема обратной связи" дважды отмечено, что анонимность — один из двух ключевых принципов СОП (наравне с обязательностью). - В регламенте (Content 3) подтверждается, что комментарии очищаются от личных данных перед передачей преподавателям, а оценка преподавателями происходит только по обобщенным статистическим данным. - Также указано, что результаты СОП передаются преподавателям только после начала следующего модуля, что исключает возможность связи оценок с конкретными студентами.</t>
+        </is>
+      </c>
+      <c r="R34" t="n">
+        <v>21.603408</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="n">
+        <v>45</v>
+      </c>
+      <c r="U34" t="n">
+        <v>9</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0.9777777777777777</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0.1962751299142838</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0.3209525942802429</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0.4827722907066345</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>17.40818822634936</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0.5175073742866516</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0.391403466463089</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.2733136713504791</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Студент</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Бакалавриат</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Цифровые системы</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Как зайти в SmartLMS?</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>['Москва', 'бакалавриат']</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>['Цифровые системы']</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>['https://www.hse.ru/studyspravka/start', 'file_365.docx', 'Деньги', 'Учебный процесс', 'Цифровые системы', 'Безопасность', 'Социальные вопросы', 'ВУЦ', 'https://www.hse.ru/studyspravka/start', 'file_365.docx', 'Деньги', 'Учебный процесс', 'Цифровые системы', 'Безопасность', 'Социальные вопросы', 'ВУЦ', 'https://www.hse.ru/studyspravka/zachetbook', 'file_554.docx', 'Учебный процесс', 'Цифровые системы', 'https://www.hse.ru/studyspravka/zachetbook', 'file_554.docx', 'Учебный процесс', 'Цифровые системы']</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Для входа в SmartLMS используйте логин от корпоративной почты (*ваш_логин@edu.hse.ru*) и пароль от неё. Например, если ваш логин в системе НИУ ВШЭ — *ivanovii*, то для авторизации введите *ivanovii@edu.hse.ru*. Ссылка на SmartLMS: [smartlms.hse.ru](https://smartlms.hse.ru).  Подробнее: https://www.hse.ru/studyspravka/start</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Начало учебы в Вышке (Москва) Начало учебы в Вышке Поздравляем с началом обучения в НИУ ВШЭ-Москва! Ниже приведена основная информация, которая будет полезна в самом начале обучения. Внимательно ознакомьтесь с ней, и влиться в учебу будет гораздо легче! Вот первые шаги, которые необходимо выполнить: Подписать и сдать лист ознакомления с регламентами НИУ ВШЭ и согласие на обработку персональных данных Изучите правила университета . Распечатайте листы в одном экземпляре каждый, подпишите и сдайте в учебный офис своей образовательной программы ✅ Согласие на обработку персональных данных Согласие на обработку персональных данных 18- [https://www.hse.ru/mirror/pubs/share/856720243.doc] (нет 18 лет) Согласие на обработку персональных данных 18+ [https://www.hse.ru/mirror/pubs/share/856720245.doc] (исполнилось 18 лет) ✅ Лист ознакомления с правилами ВШЭ Лист ознакомления с регламентами [https://www.hse.ru/mirror/pubs/share/856720247.pdf] Получить студенческий билет Для получения студенческого</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>['https://www.hse.ru/studyspravka/start', 'https://www.hse.ru/studyspravka/start', 'https://www.hse.ru/mirror/pubs/share/856720243.doc]', 'https://www.hse.ru/mirror/pubs/share/856720245.doc]', 'https://www.hse.ru/mirror/pubs/share/856720247.pdf]', 'https://vk.com/hselibrary]', 'https://t.me/s/hse_library/]', 'https://www.mos.ru/socialnaya-karta/services-proverka-grazhdanina-v-reestre-studentov/]', 'http://www.mos.ru/]', 'https://www.mos.ru/karta-moskvicha/services-proverka-sostojanija-izgotovlenija-karty-moskvicha/]', 'https://www.hse.ru/org/hse/ouk/mil/', 'https://ivisa.hse', 'https://www.hse.ru/studyspravka/zachetbook', 'https://www.hse.ru/studyspravka/zachetbook']</t>
+        </is>
+      </c>
+      <c r="M35" t="n">
+        <v>4</v>
+      </c>
+      <c r="N35" t="n">
+        <v>4</v>
+      </c>
+      <c r="O35" t="n">
+        <v>35</v>
+      </c>
+      <c r="P35" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>В контексте явно указано, что для авторизации в SmartLMS студенты используют логин в формате *login@edu.hse.ru* и пароль от корпоративной электронной почты (Content 1, Content 3). Эта инструкция напрямую отвечает на вопрос, дополнительные источники подтверждают метод входа. Процедура стандартна, альтернативных способов в предоставленных данных не упоминается.</t>
+        </is>
+      </c>
+      <c r="R35" t="n">
+        <v>9.913263000000001</v>
+      </c>
+      <c r="S35" t="n">
+        <v>9</v>
+      </c>
+      <c r="T35" t="n">
+        <v>41</v>
+      </c>
+      <c r="U35" t="n">
+        <v>4.555555555555555</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0.7073170731707317</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0.4307425022125244</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0.3262155055999756</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>0.2430419623851776</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>12.8749497449551</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0.5712954998016357</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0.5669274926185608</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.4112316370010376</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Студент</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Бакалавриат</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Цифровые системы</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>А в чем разница между LMS и SmartLMS?</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>['Москва', 'бакалавриат']</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>['Цифровые системы']</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>['https://www.hse.ru/studyspravka/start', 'file_365.docx', 'Деньги', 'Учебный процесс', 'Цифровые системы', 'Безопасность', 'Социальные вопросы', 'ВУЦ', 'https://www.hse.ru/studyspravka/start', 'file_365.docx', 'Деньги', 'Учебный процесс', 'Цифровые системы', 'Безопасность', 'Социальные вопросы', 'ВУЦ', 'https://www.hse.ru/studyspravka/start', 'file_365.docx', 'Деньги', 'Учебный процесс', 'Цифровые системы', 'Безопасность', 'Социальные вопросы', 'ВУЦ']</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>**LMS** — базовая система управления обучением с доступом к учебным дисциплинам, индивидуальному плану и электронной зачётной книжке. **SmartLMS** — усовершенствованная платформа для взаимодействия: преподаватели публикуют материалы и задания, студенты загружают работы. Авторизация производится через логин/пароль корпоративной почты (@edu.hse.ru). Обе системы доступны через [Единый личный кабинет](https://lk.hse.ru/). Для уточнения функционала конкретной платформы обратитесь в учебный офис своей программы.  Подробнее: https://www.hse.ru/studyspravka/start</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Здесь расположена «выразительная кнопка», социальные и административные сервисы для студентов. А ещё в личном кабинете можно управлять своими подписками на анонсы мероприятий университета, чтобы быть в курсе последних событий. LMS — это единое образовательное пространство первого поколения. Каждый студент при входе в LMS попадает в свой личный кабинет, в котором он увидит список всех учебных дисциплин, которые назначены для изучения в соответствии с индивидуальным учебным планом. Здесь же находится электронная зачетная книжка.</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>['https://www.hse.ru/studyspravka/start', 'https://www.hse.ru/studyspravka/start', 'https://www.hse.ru/mirror/pubs/share/856720243.doc]', 'https://www.hse.ru/mirror/pubs/share/856720245.doc]', 'https://www.hse.ru/mirror/pubs/share/856720247.pdf]', 'https://vk.com/hselibrary]', 'https://t.me/s/hse_library/]', 'https://www.mos.ru/socialnaya-karta/services-proverka-grazhdanina-v-reestre-studentov/]', 'http://www.mos.ru/]', 'https://www.mos.ru/karta-moskvicha/services-proverka-sostojanija-izgotovlenija-karty-moskvicha/]', 'https://www.hse.ru/org/hse/ouk/mil/', 'https://ivisa.hse', 'https://www.hse.ru/studyspravka/start']</t>
+        </is>
+      </c>
+      <c r="M36" t="n">
+        <v>8</v>
+      </c>
+      <c r="N36" t="n">
+        <v>3</v>
+      </c>
+      <c r="O36" t="n">
+        <v>58</v>
+      </c>
+      <c r="P36" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>В предоставленных контекстах четко обозначены различия между системами: - LMS позиционируется как образовательное пространство первого поколения с личным кабинетом для просмотра учебных дисциплин, индивидуального учебного плана и электронной зачётной книжки (Content 3-C); - SmartLMS описывается как обновлённая платформа для взаимодействия всех участников учебного процесса: загрузки материалов курсов преподавателями, выполнения и сдачи заданий студентами. Авторизация осуществляется через логин и пароль корпоративной почты (Content SmartLMS).</t>
+        </is>
+      </c>
+      <c r="R36" t="n">
+        <v>30.143864</v>
+      </c>
+      <c r="S36" t="n">
+        <v>7</v>
+      </c>
+      <c r="T36" t="n">
+        <v>58</v>
+      </c>
+      <c r="U36" t="n">
+        <v>8.285714285714286</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0.9482758620689655</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0.3272179663181305</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0.6189069151878357</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0.05387512966990471</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>25.19814685445158</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0.5775376558303833</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0.6214766502380371</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.209854930639267</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/result.xlsx
+++ b/data/result.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF4"/>
+  <dimension ref="A1:AF8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -959,6 +959,496 @@
         <v>0.2732588648796082</v>
       </c>
       <c r="AF4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Студент</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Нижний Новгород</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Бакалавриат</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Учебный процесс</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Я хочу просто тебя протестить</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>['Нижний Новгород', 'бакалавриат']</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>['Учебный процесс']</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>['https://nnov.hse.ru/library/booking', 'file_153.docx', 'Учебный процесс', 'Наука', 'https://www.hse.ru/studyspravka/acmob', 'file_133.docx', 'Деньги', 'Учебный процесс', 'Траектории обучения', 'Перемещения студентов / Изменения статусов студентов', 'https://www.hse.ru/org/hse/elective_courses/MN_OI', 'file_280.docx', 'Учебный процесс', 'Траектории обучения', 'https://nnov.hse.ru/library/access', 'file_157.docx', 'Учебный процесс', 'Наука']</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Мне кажется неуместно здесь это обсуждать. Моя цель — проконсультировать тебя по вопросам обучения. Может, у тебя есть еще какие-то вопросы?</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Cleaned context is empty, getting info from page contents in contexts: Спасибо за участие! Сервис предназначен только для отправки сообщений об орфографических и пунктуационных ошибках. /noindex Выделите её, нажмите Ctrl+Enter и отправьте нам уведомление. Спасибо за участие! Сервис предназначен только для отправки сообщений об орфографических и пунктуационных ошибках. /noindex Выделите её, нажмите Ctrl+Enter и отправьте нам уведомление. Спасибо за участие! Сервис предназначен только для отправки сообщений об орфографических и пунктуационных ошибках. /noindex Выделите её, нажмите Ctrl+Enter и отправьте нам уведомление. Спасибо за участие! Сервис предназначен только для отправки сообщений об орфографических и пунктуационных ошибках. /noindex</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>2025-07-31 12:32:08</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>['https://nnov.hse', 'https://www.hse.ru/studyspravka/acmob', 'https://www.hse.ru/org/hse/elective_courses/MN_OI', 'https://nnov.hse']</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>5</v>
+      </c>
+      <c r="O5" t="n">
+        <v>4</v>
+      </c>
+      <c r="P5" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q5" t="b">
+        <v>0</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="n">
+        <v>6.740556</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>21</v>
+      </c>
+      <c r="V5" t="n">
+        <v>7</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.9523809523809523</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.05505134165287018</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.9232057332992554</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.02174292132258415</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>5.444538009475098</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.4579519629478455</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.5695139169692993</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.4845642447471619</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Студент</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Нижний Новгород</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Бакалавриат</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Учебный процесс</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Когда будут экзамены</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>['Нижний Новгород', 'бакалавриат']</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>['Учебный процесс']</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>['https://www.hse.ru/dataculture/exams', 'file_4.docx', 'Учебный процесс', 'Траектории обучения', 'Цифровые компетенции', 'https://www.hse.ru/studyspravka/otch', 'file_404.docx', 'Деньги', 'Учебный процесс', 'ГИА', 'Перемещения студентов / Изменения статусов студентов', 'https://www.hse.ru/studyspravka/rate', 'file_458.docx', 'Деньги', 'Учебный процесс', 'Перемещения студентов / Изменения статусов студентов', 'Цифровые системы', 'Социальные вопросы', 'https://www.hse.ru/docs/981357423.html', 'file_33.docx', 'Учебный процесс', 'Траектории обучения', 'Английский язык', 'Перемещения студентов / Изменения статусов студентов', 'Дополнительное образование']</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Точные даты экзаменов зависят от вашей образовательной программы, года поступления и дисциплин. 1. Проверяйте расписание в **[электронной зачётке LMS](https://lms.hse.ru/index.php?page=gradebook)** или на сайте вашего учебного подразделения — публикуется не позднее чем за 3 дня до сессии. 2. Для Независимого экзамена по цифровой грамотности (только для определённых программ) регистрация начинается с 1 февраля 2025. 3. Студенты 2024 года сдают основные экзамены во 2-м полугодии (3-4 модули) 2025-2026 учебного года. Если возникли сложности — обратитесь в учебный офис вашей программы.  Упоминается в ссылках ниже: https://www.hse.ru/dataculture/exams</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>В резервные дни экзамены сдают студенты: Которые не смогли по уважительной причине сдать экзамены в назначенное ранее время; Чьи работы были аннулированы с предоставлением возможности написать экзамен в резервный день. Независимый экзамен по цифровой грамотности в 2024/2025 учебном году начнет проводиться с 1 февраля 2025 года. Язык проведения экзаменов Cтуденты программ, реализуемых только на английском языке или на двух языках, сдают на английском языке; Остальные студенты сдают на русском языке.</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>2025-07-31 12:33:49</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>['https://www.hse.ru/dataculture/exams', 'https://www.hse.ru/studyspravka/otch', 'https://www.hse.ru/studyspravka/rate', 'https://www.hse.ru/docs/981357423.html']</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>3</v>
+      </c>
+      <c r="O6" t="n">
+        <v>4</v>
+      </c>
+      <c r="P6" t="n">
+        <v>82</v>
+      </c>
+      <c r="Q6" t="b">
+        <v>1</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>В предоставленных контекстах указано: - Расписание экзаменов публикуется на специализированном разделе сайта не менее чем за **3 календарных дня** до начала и доступно в LMS (электронной зачётке). - Для Независимого экзамена по цифровой грамотности (2024/2025 учебный год) дата начала — **1 февраля 2025**, а студенты самостоятельно записываются через Центр независимой экспертизы Школы иностранных языков. - Сроки зависят от года набора (например, студенты 2024 года сдают во **2-м полугодии 2025-2026**, студенты 2025 года — до конца сессии **2 модуля 2 курса**). - Экзамены проводятся **во время сессии или в течение 10 дней до неё**. Резервные дни предназначены для пересдач по уважительным причинам. Однако конкретные календарные даты не указаны — они индивидуальны для каждой дисциплины и программы.</t>
+        </is>
+      </c>
+      <c r="S6" t="n">
+        <v>8.788527999999999</v>
+      </c>
+      <c r="T6" t="n">
+        <v>9</v>
+      </c>
+      <c r="U6" t="n">
+        <v>82</v>
+      </c>
+      <c r="V6" t="n">
+        <v>9.111111111111111</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.8414634146341463</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.3441371619701385</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.5401543378829956</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.1157085001468658</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>28.31651182182246</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.5926027297973633</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.1955909579992294</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.05555555555555555</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.3722919225692749</v>
+      </c>
+      <c r="AF6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Студент</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Нижний Новгород</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Бакалавриат</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Внеучебка</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Как создать свой клуб</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>['Нижний Новгород', 'бакалавриат']</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>['Внеучебка']</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>['https://www.hse.ru/docs/552119473.html', 'file_107.docx', 'Деньги', 'Социальные вопросы', 'Внеучебка', 'https://www.hse.ru/docs/552119473.html', 'file_107.docx', 'Деньги', 'Социальные вопросы', 'Внеучебка', 'https://www.hse.ru/docs/239587638.html', 'file_115.docx', 'Учебный процесс', 'Внеучебка', 'https://www.hse.ru/docs/552119473.html', 'file_108.docx', 'Деньги', 'Социальные вопросы', 'Внеучебка']</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Информация о создании студенческого клуба не обнаружена в предоставленных материалах. Рекомендую обратиться в учебный офис вашей образовательной программы или в отдел внеучебной деятельности НИУ ВШЭ. Они смогут подсказать процедуру и условия регистрации новых студенческих инициатив.  Упоминается в ссылках ниже: https://www.hse.ru/docs/552119473.html</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Приложение к приказу НИУ ВШЭ от 21.12.2022 № 6.18.1-01/211222-13 УТВЕРЖДЕНО ученым советом НИУ ВШЭ протокол от 30.11.2022 № 11 Положение</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>2025-07-31 12:39:47</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>['https://www.hse.ru/docs/552119473.html', 'https://www.hse.ru/docs/552119473.html', 'https://www.hse.ru/docs/239587638.html', 'https://www.hse.ru/docs/552119473.html']</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>4</v>
+      </c>
+      <c r="O7" t="n">
+        <v>4</v>
+      </c>
+      <c r="P7" t="n">
+        <v>40</v>
+      </c>
+      <c r="Q7" t="b">
+        <v>1</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Предоставленные контексты содержат информацию о положении конкурса ИИ-решений выпускных работ, скидках на программы повышения квалификации и профессиональной переподготовки. Однако отсутствуют данные о процедуре создания студенческого клуба или внеучебных объединений в НИУ ВШЭ. Нет упоминаний о требованиях, документах или ресурсах, связанных с организацией клубов.</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
+        <v>10.519907</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>39</v>
+      </c>
+      <c r="V7" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.1006272360682487</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.7604485750198364</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0.1389241814613342</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>8.162420626687009</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.5042080879211426</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.2574115395545959</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.2018103301525116</v>
+      </c>
+      <c r="AF7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Студент</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Нижний Новгород</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Бакалавриат</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Внеучебка</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Хочу записаться в клуб по саберфайтингу</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>['Нижний Новгород', 'бакалавриат']</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>['Внеучебка']</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>['https://www.hse.ru/docs/239587638.html', 'file_115.docx', 'Учебный процесс', 'Внеучебка', 'https://www.hse.ru/docs/239587638.html', 'file_115.docx', 'Учебный процесс', 'Внеучебка', 'https://www.hse.ru/docs/239587638.html', 'file_115.docx', 'Учебный процесс', 'Внеучебка', 'https://www.hse.ru/docs/552119473.html', 'file_108.docx', 'Деньги', 'Социальные вопросы', 'Внеучебка']</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>К сожалению, информации о клубе по саберфайтингу в предоставленных материалах нет. Рекомендую: 1. Проверить раздел о студенческих инициативах на [официальном сайте НИУ ВШЭ](https://www.hse.ru/). 2. Написать в учебный офис своей программы или Центр организации студенческих проектов. 3. Изучить объявления в корпоративной почте/LMS — там часто публикуют информацию о новых клубах.  Упоминается в ссылках ниже: https://www.hse.ru/docs/239587638.html</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>по образовательным программам высшего образования по итогам обучения в Лицее НИУ ВШЭ и по итогам обучения в Физико-математической школе МИЭМ НИУ ВШЭ в соответствии с разделом IV настоящего положения;</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>2025-07-31 12:49:52</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>['https://www.hse.ru/docs/239587638.html', 'https://www.hse.ru/docs/239587638.html', 'https://www.hse.ru/docs/239587638.html', 'https://www.hse.ru/docs/552119473.html']</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>6</v>
+      </c>
+      <c r="O8" t="n">
+        <v>4</v>
+      </c>
+      <c r="P8" t="n">
+        <v>54</v>
+      </c>
+      <c r="Q8" t="b">
+        <v>1</v>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>В предоставленных контекстах отсутствует какая-либо информация о клубах, секциях или внеучебной деятельности НИУ ВШЭ, включая саберфайтинг. Упомянутые отрывки касаются скидок на образовательные программы, требований к стажу и формальных документов, не связанных с тематикой вопроса. Анализ содержимого не выявил даже косвенных упоминаний студенческих объединений.</t>
+        </is>
+      </c>
+      <c r="S8" t="n">
+        <v>7.548112</v>
+      </c>
+      <c r="T8" t="n">
+        <v>7</v>
+      </c>
+      <c r="U8" t="n">
+        <v>53</v>
+      </c>
+      <c r="V8" t="n">
+        <v>7.571428571428571</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.1192905679345131</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.7646540403366089</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.1160553321242332</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>14.88137153017895</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.5217061638832092</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.5049881339073181</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.2274675965309143</v>
+      </c>
+      <c r="AF8" t="b">
         <v>0</v>
       </c>
     </row>
